--- a/Report JSS 1D.xlsx
+++ b/Report JSS 1D.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\PythonSetup\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" tabRatio="771" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -19,7 +24,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="5">Report!$A$2:$N$57</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -2086,23 +2091,49 @@
     <xf numFmtId="0" fontId="44" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment textRotation="90"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2119,26 +2150,67 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2167,55 +2239,6 @@
     <xf numFmtId="49" fontId="20" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" textRotation="90" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2227,27 +2250,6 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2257,6 +2259,9 @@
     <xf numFmtId="0" fontId="45" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Hyperlink" xfId="12" builtinId="8"/>
@@ -3277,7 +3282,7 @@
         <xdr:cNvPr id="4" name="TextBox 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000004000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3368,7 +3373,7 @@
         <xdr:cNvPr id="5" name="TextBox 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000005000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3464,7 +3469,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0600-000007000000}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -9234,14 +9239,14 @@
   <sheetData>
     <row r="1" spans="1:216">
       <c r="A1" s="43"/>
-      <c r="B1" s="223" t="s">
+      <c r="B1" s="225" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
+      <c r="C1" s="225"/>
+      <c r="D1" s="225"/>
+      <c r="E1" s="225"/>
+      <c r="F1" s="225"/>
+      <c r="G1" s="225"/>
       <c r="H1" s="51"/>
       <c r="I1" s="51"/>
       <c r="J1" s="52"/>
@@ -9250,28 +9255,28 @@
       <c r="M1" s="43"/>
       <c r="N1" s="58"/>
       <c r="O1" s="57"/>
-      <c r="P1" s="227" t="s">
+      <c r="P1" s="230" t="s">
         <v>36</v>
       </c>
-      <c r="Q1" s="228"/>
-      <c r="R1" s="228"/>
-      <c r="S1" s="228"/>
-      <c r="T1" s="228"/>
-      <c r="U1" s="228"/>
-      <c r="V1" s="228"/>
+      <c r="Q1" s="231"/>
+      <c r="R1" s="231"/>
+      <c r="S1" s="231"/>
+      <c r="T1" s="231"/>
+      <c r="U1" s="231"/>
+      <c r="V1" s="231"/>
       <c r="W1" s="59"/>
       <c r="X1" s="59"/>
       <c r="Y1" s="56"/>
       <c r="Z1" s="81"/>
-      <c r="AA1" s="217" t="s">
+      <c r="AA1" s="226" t="s">
         <v>101</v>
       </c>
-      <c r="AB1" s="217"/>
-      <c r="AC1" s="217"/>
-      <c r="AD1" s="217"/>
-      <c r="AE1" s="217"/>
-      <c r="AF1" s="217"/>
-      <c r="AG1" s="217"/>
+      <c r="AB1" s="226"/>
+      <c r="AC1" s="226"/>
+      <c r="AD1" s="226"/>
+      <c r="AE1" s="226"/>
+      <c r="AF1" s="226"/>
+      <c r="AG1" s="226"/>
       <c r="AH1" s="81"/>
       <c r="AI1" s="81"/>
       <c r="AJ1" s="81"/>
@@ -9291,197 +9296,197 @@
       <c r="AV1" s="46"/>
       <c r="AW1" s="3"/>
       <c r="AX1" s="87"/>
-      <c r="AY1" s="224" t="s">
+      <c r="AY1" s="227" t="s">
         <v>93</v>
       </c>
-      <c r="AZ1" s="224"/>
-      <c r="BA1" s="224"/>
-      <c r="BB1" s="224"/>
-      <c r="BC1" s="224"/>
-      <c r="BD1" s="224"/>
-      <c r="BE1" s="224"/>
+      <c r="AZ1" s="227"/>
+      <c r="BA1" s="227"/>
+      <c r="BB1" s="227"/>
+      <c r="BC1" s="227"/>
+      <c r="BD1" s="227"/>
+      <c r="BE1" s="227"/>
       <c r="BF1" s="87"/>
       <c r="BG1" s="87"/>
       <c r="BH1" s="87"/>
       <c r="BI1" s="3"/>
       <c r="BJ1" s="92"/>
-      <c r="BK1" s="225" t="s">
+      <c r="BK1" s="228" t="s">
         <v>64</v>
       </c>
-      <c r="BL1" s="226"/>
-      <c r="BM1" s="226"/>
-      <c r="BN1" s="226"/>
-      <c r="BO1" s="226"/>
-      <c r="BP1" s="226"/>
-      <c r="BQ1" s="226"/>
+      <c r="BL1" s="229"/>
+      <c r="BM1" s="229"/>
+      <c r="BN1" s="229"/>
+      <c r="BO1" s="229"/>
+      <c r="BP1" s="229"/>
+      <c r="BQ1" s="229"/>
       <c r="BR1" s="92"/>
       <c r="BS1" s="92"/>
       <c r="BT1" s="92"/>
       <c r="BU1" s="3"/>
       <c r="BV1" s="97"/>
-      <c r="BW1" s="218" t="s">
+      <c r="BW1" s="232" t="s">
         <v>87</v>
       </c>
-      <c r="BX1" s="218"/>
-      <c r="BY1" s="218"/>
-      <c r="BZ1" s="218"/>
-      <c r="CA1" s="218"/>
-      <c r="CB1" s="218"/>
-      <c r="CC1" s="218"/>
+      <c r="BX1" s="232"/>
+      <c r="BY1" s="232"/>
+      <c r="BZ1" s="232"/>
+      <c r="CA1" s="232"/>
+      <c r="CB1" s="232"/>
+      <c r="CC1" s="232"/>
       <c r="CD1" s="97"/>
       <c r="CE1" s="97"/>
       <c r="CF1" s="97"/>
       <c r="CG1" s="3"/>
       <c r="CH1" s="66"/>
-      <c r="CI1" s="219" t="s">
+      <c r="CI1" s="233" t="s">
         <v>88</v>
       </c>
-      <c r="CJ1" s="219"/>
-      <c r="CK1" s="219"/>
-      <c r="CL1" s="219"/>
-      <c r="CM1" s="219"/>
-      <c r="CN1" s="219"/>
-      <c r="CO1" s="219"/>
+      <c r="CJ1" s="233"/>
+      <c r="CK1" s="233"/>
+      <c r="CL1" s="233"/>
+      <c r="CM1" s="233"/>
+      <c r="CN1" s="233"/>
+      <c r="CO1" s="233"/>
       <c r="CP1" s="66"/>
       <c r="CQ1" s="66"/>
       <c r="CR1" s="66"/>
       <c r="CS1" s="3"/>
       <c r="CT1" s="71"/>
-      <c r="CU1" s="220" t="s">
+      <c r="CU1" s="234" t="s">
         <v>67</v>
       </c>
-      <c r="CV1" s="220"/>
-      <c r="CW1" s="220"/>
-      <c r="CX1" s="220"/>
-      <c r="CY1" s="220"/>
-      <c r="CZ1" s="220"/>
-      <c r="DA1" s="220"/>
+      <c r="CV1" s="234"/>
+      <c r="CW1" s="234"/>
+      <c r="CX1" s="234"/>
+      <c r="CY1" s="234"/>
+      <c r="CZ1" s="234"/>
+      <c r="DA1" s="234"/>
       <c r="DB1" s="71"/>
       <c r="DC1" s="71"/>
       <c r="DD1" s="71"/>
       <c r="DE1" s="3"/>
       <c r="DF1" s="58"/>
-      <c r="DG1" s="221" t="s">
+      <c r="DG1" s="235" t="s">
         <v>89</v>
       </c>
-      <c r="DH1" s="221"/>
-      <c r="DI1" s="221"/>
-      <c r="DJ1" s="221"/>
-      <c r="DK1" s="221"/>
-      <c r="DL1" s="221"/>
-      <c r="DM1" s="221"/>
+      <c r="DH1" s="235"/>
+      <c r="DI1" s="235"/>
+      <c r="DJ1" s="235"/>
+      <c r="DK1" s="235"/>
+      <c r="DL1" s="235"/>
+      <c r="DM1" s="235"/>
       <c r="DN1" s="58"/>
       <c r="DO1" s="58"/>
       <c r="DP1" s="58"/>
       <c r="DQ1" s="3"/>
       <c r="DR1" s="107"/>
-      <c r="DS1" s="222" t="s">
+      <c r="DS1" s="236" t="s">
         <v>90</v>
       </c>
-      <c r="DT1" s="222"/>
-      <c r="DU1" s="222"/>
-      <c r="DV1" s="222"/>
-      <c r="DW1" s="222"/>
-      <c r="DX1" s="222"/>
-      <c r="DY1" s="222"/>
+      <c r="DT1" s="236"/>
+      <c r="DU1" s="236"/>
+      <c r="DV1" s="236"/>
+      <c r="DW1" s="236"/>
+      <c r="DX1" s="236"/>
+      <c r="DY1" s="236"/>
       <c r="DZ1" s="107"/>
       <c r="EA1" s="107"/>
       <c r="EB1" s="107"/>
       <c r="EC1" s="3"/>
       <c r="ED1" s="76"/>
-      <c r="EE1" s="214" t="s">
+      <c r="EE1" s="239" t="s">
         <v>65</v>
       </c>
-      <c r="EF1" s="214"/>
-      <c r="EG1" s="214"/>
-      <c r="EH1" s="214"/>
-      <c r="EI1" s="214"/>
-      <c r="EJ1" s="214"/>
-      <c r="EK1" s="214"/>
+      <c r="EF1" s="239"/>
+      <c r="EG1" s="239"/>
+      <c r="EH1" s="239"/>
+      <c r="EI1" s="239"/>
+      <c r="EJ1" s="239"/>
+      <c r="EK1" s="239"/>
       <c r="EL1" s="76"/>
       <c r="EM1" s="76"/>
       <c r="EN1" s="76"/>
       <c r="EO1" s="3"/>
       <c r="EP1" s="102"/>
-      <c r="EQ1" s="215" t="s">
+      <c r="EQ1" s="240" t="s">
         <v>68</v>
       </c>
-      <c r="ER1" s="215"/>
-      <c r="ES1" s="215"/>
-      <c r="ET1" s="215"/>
-      <c r="EU1" s="215"/>
-      <c r="EV1" s="215"/>
-      <c r="EW1" s="215"/>
+      <c r="ER1" s="240"/>
+      <c r="ES1" s="240"/>
+      <c r="ET1" s="240"/>
+      <c r="EU1" s="240"/>
+      <c r="EV1" s="240"/>
+      <c r="EW1" s="240"/>
       <c r="EX1" s="102"/>
       <c r="EY1" s="102"/>
       <c r="EZ1" s="102"/>
       <c r="FA1" s="3"/>
       <c r="FB1" s="118"/>
-      <c r="FC1" s="213" t="s">
+      <c r="FC1" s="238" t="s">
         <v>66</v>
       </c>
-      <c r="FD1" s="213"/>
-      <c r="FE1" s="213"/>
-      <c r="FF1" s="213"/>
-      <c r="FG1" s="213"/>
-      <c r="FH1" s="213"/>
-      <c r="FI1" s="213"/>
+      <c r="FD1" s="238"/>
+      <c r="FE1" s="238"/>
+      <c r="FF1" s="238"/>
+      <c r="FG1" s="238"/>
+      <c r="FH1" s="238"/>
+      <c r="FI1" s="238"/>
       <c r="FJ1" s="118"/>
       <c r="FK1" s="118"/>
       <c r="FL1" s="118"/>
       <c r="FM1" s="3"/>
       <c r="FN1" s="52"/>
-      <c r="FO1" s="216" t="s">
+      <c r="FO1" s="241" t="s">
         <v>94</v>
       </c>
-      <c r="FP1" s="216"/>
-      <c r="FQ1" s="216"/>
-      <c r="FR1" s="216"/>
-      <c r="FS1" s="216"/>
-      <c r="FT1" s="216"/>
-      <c r="FU1" s="216"/>
+      <c r="FP1" s="241"/>
+      <c r="FQ1" s="241"/>
+      <c r="FR1" s="241"/>
+      <c r="FS1" s="241"/>
+      <c r="FT1" s="241"/>
+      <c r="FU1" s="241"/>
       <c r="FV1" s="52"/>
       <c r="FW1" s="52"/>
       <c r="FX1" s="52"/>
       <c r="FY1" s="3"/>
       <c r="FZ1" s="81"/>
-      <c r="GA1" s="217" t="s">
+      <c r="GA1" s="226" t="s">
         <v>95</v>
       </c>
-      <c r="GB1" s="217"/>
-      <c r="GC1" s="217"/>
-      <c r="GD1" s="217"/>
-      <c r="GE1" s="217"/>
-      <c r="GF1" s="217"/>
-      <c r="GG1" s="217"/>
+      <c r="GB1" s="226"/>
+      <c r="GC1" s="226"/>
+      <c r="GD1" s="226"/>
+      <c r="GE1" s="226"/>
+      <c r="GF1" s="226"/>
+      <c r="GG1" s="226"/>
       <c r="GH1" s="81"/>
       <c r="GI1" s="81"/>
       <c r="GJ1" s="81"/>
       <c r="GK1" s="3"/>
       <c r="GL1" s="118"/>
-      <c r="GM1" s="213" t="s">
+      <c r="GM1" s="238" t="s">
         <v>63</v>
       </c>
-      <c r="GN1" s="213"/>
-      <c r="GO1" s="213"/>
-      <c r="GP1" s="213"/>
-      <c r="GQ1" s="213"/>
-      <c r="GR1" s="213"/>
-      <c r="GS1" s="213"/>
+      <c r="GN1" s="238"/>
+      <c r="GO1" s="238"/>
+      <c r="GP1" s="238"/>
+      <c r="GQ1" s="238"/>
+      <c r="GR1" s="238"/>
+      <c r="GS1" s="238"/>
       <c r="GT1" s="118"/>
       <c r="GU1" s="118"/>
       <c r="GV1" s="118"/>
       <c r="GW1" s="3"/>
       <c r="GX1" s="112"/>
-      <c r="GY1" s="212" t="s">
+      <c r="GY1" s="237" t="s">
         <v>83</v>
       </c>
-      <c r="GZ1" s="212"/>
-      <c r="HA1" s="212"/>
-      <c r="HB1" s="212"/>
-      <c r="HC1" s="212"/>
-      <c r="HD1" s="212"/>
-      <c r="HE1" s="212"/>
+      <c r="GZ1" s="237"/>
+      <c r="HA1" s="237"/>
+      <c r="HB1" s="237"/>
+      <c r="HC1" s="237"/>
+      <c r="HD1" s="237"/>
+      <c r="HE1" s="237"/>
       <c r="HF1" s="112"/>
       <c r="HG1" s="112"/>
       <c r="HH1" s="112"/>
@@ -26984,7 +26989,7 @@
         <v>10</v>
       </c>
       <c r="AB27" s="136">
-        <v>66</v>
+        <v>6</v>
       </c>
       <c r="AC27" s="136">
         <v>10</v>
@@ -26994,14 +26999,14 @@
       </c>
       <c r="AE27" s="81">
         <f t="shared" si="91"/>
-        <v>96</v>
+        <v>36</v>
       </c>
       <c r="AF27" s="136">
         <v>48</v>
       </c>
       <c r="AG27" s="81">
         <f t="shared" si="12"/>
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="AH27" s="81">
         <f t="shared" si="13"/>
@@ -43729,16 +43734,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="AA1:AG1"/>
-    <mergeCell ref="AY1:BE1"/>
-    <mergeCell ref="BK1:BQ1"/>
-    <mergeCell ref="P1:V1"/>
-    <mergeCell ref="BW1:CC1"/>
-    <mergeCell ref="CI1:CO1"/>
-    <mergeCell ref="CU1:DA1"/>
-    <mergeCell ref="DG1:DM1"/>
-    <mergeCell ref="DS1:DY1"/>
     <mergeCell ref="GY1:HE1"/>
     <mergeCell ref="GM1:GS1"/>
     <mergeCell ref="EE1:EK1"/>
@@ -43746,6 +43741,16 @@
     <mergeCell ref="FC1:FI1"/>
     <mergeCell ref="FO1:FU1"/>
     <mergeCell ref="GA1:GG1"/>
+    <mergeCell ref="BW1:CC1"/>
+    <mergeCell ref="CI1:CO1"/>
+    <mergeCell ref="CU1:DA1"/>
+    <mergeCell ref="DG1:DM1"/>
+    <mergeCell ref="DS1:DY1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="AA1:AG1"/>
+    <mergeCell ref="AY1:BE1"/>
+    <mergeCell ref="BK1:BQ1"/>
+    <mergeCell ref="P1:V1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -43907,114 +43912,114 @@
       <c r="A10" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="263" t="str">
+      <c r="B10" s="242" t="str">
         <f>VLOOKUP(B14,Data!A1:I52,2,0)</f>
-        <v>MOHAMMED FATIMA NGGANJUWA</v>
-      </c>
-      <c r="C10" s="263"/>
-      <c r="D10" s="263"/>
-      <c r="E10" s="263"/>
-      <c r="F10" s="263"/>
-      <c r="G10" s="263"/>
+        <v>ABBA FATIMA NGURU</v>
+      </c>
+      <c r="C10" s="242"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="242"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
-      <c r="K10" s="261" t="s">
+      <c r="K10" s="243" t="s">
         <v>38</v>
       </c>
-      <c r="L10" s="261"/>
-      <c r="M10" s="263" t="str">
+      <c r="L10" s="243"/>
+      <c r="M10" s="242" t="str">
         <f>VLOOKUP(B14,Data!A2:H52,7,0)</f>
         <v>2nd</v>
       </c>
-      <c r="N10" s="264"/>
+      <c r="N10" s="244"/>
     </row>
     <row r="11" spans="1:14" ht="18" customHeight="1">
       <c r="A11" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="261">
+      <c r="B11" s="243">
         <f>VLOOKUP(B14,Data!A2:H52,4,0)</f>
-        <v>13</v>
-      </c>
-      <c r="C11" s="261"/>
-      <c r="D11" s="261"/>
-      <c r="E11" s="261"/>
-      <c r="F11" s="261"/>
-      <c r="G11" s="261"/>
+        <v>10</v>
+      </c>
+      <c r="C11" s="243"/>
+      <c r="D11" s="243"/>
+      <c r="E11" s="243"/>
+      <c r="F11" s="243"/>
+      <c r="G11" s="243"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="J11" s="31"/>
-      <c r="K11" s="261" t="s">
+      <c r="K11" s="243" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="261"/>
-      <c r="M11" s="263" t="str">
+      <c r="L11" s="243"/>
+      <c r="M11" s="242" t="str">
         <f>VLOOKUP(B14,Data!A2:H52,3,0)</f>
         <v xml:space="preserve">Jss 1D </v>
       </c>
-      <c r="N11" s="264"/>
+      <c r="N11" s="244"/>
     </row>
     <row r="12" spans="1:14" ht="18" customHeight="1">
       <c r="A12" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="263" t="str">
+      <c r="B12" s="242" t="str">
         <f>VLOOKUP(B14,Data!A2:H52,5,0)</f>
         <v>BORNO</v>
       </c>
-      <c r="C12" s="263"/>
-      <c r="D12" s="263"/>
-      <c r="E12" s="263"/>
-      <c r="F12" s="263"/>
-      <c r="G12" s="263"/>
+      <c r="C12" s="242"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="242"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="242"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="J12" s="31"/>
-      <c r="K12" s="261" t="s">
+      <c r="K12" s="243" t="s">
         <v>42</v>
       </c>
-      <c r="L12" s="261"/>
-      <c r="M12" s="263" t="str">
+      <c r="L12" s="243"/>
+      <c r="M12" s="242" t="str">
         <f>VLOOKUP(B14,Data!A2:H52,8,0)</f>
         <v>16th January, 2026</v>
       </c>
-      <c r="N12" s="264"/>
+      <c r="N12" s="244"/>
     </row>
     <row r="13" spans="1:14" ht="18" customHeight="1">
       <c r="A13" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="B13" s="263" t="str">
+      <c r="B13" s="242" t="str">
         <f>VLOOKUP(B14,Data!A2:H52,6,0)</f>
-        <v>SHANI</v>
-      </c>
-      <c r="C13" s="263"/>
-      <c r="D13" s="263"/>
-      <c r="E13" s="263"/>
-      <c r="F13" s="263"/>
-      <c r="G13" s="263"/>
+        <v>GUBIO</v>
+      </c>
+      <c r="C13" s="242"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="242"/>
       <c r="H13" s="31"/>
       <c r="I13" s="31"/>
       <c r="J13" s="31"/>
-      <c r="K13" s="261" t="s">
+      <c r="K13" s="243" t="s">
         <v>44</v>
       </c>
-      <c r="L13" s="261"/>
-      <c r="M13" s="263" t="str">
+      <c r="L13" s="243"/>
+      <c r="M13" s="242" t="str">
         <f>IF(M20&gt;=40,"Passed","Failed")</f>
         <v>Passed</v>
       </c>
-      <c r="N13" s="264"/>
+      <c r="N13" s="244"/>
     </row>
     <row r="14" spans="1:14" ht="18" customHeight="1">
       <c r="A14" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="261">
-        <v>36</v>
-      </c>
-      <c r="C14" s="261"/>
+      <c r="B14" s="243">
+        <v>25</v>
+      </c>
+      <c r="C14" s="243"/>
       <c r="D14" s="32"/>
       <c r="E14" s="32"/>
       <c r="F14" s="32"/>
@@ -44022,10 +44027,10 @@
       <c r="H14" s="31"/>
       <c r="I14" s="31"/>
       <c r="J14" s="31"/>
-      <c r="K14" s="262"/>
-      <c r="L14" s="262"/>
-      <c r="M14" s="263"/>
-      <c r="N14" s="264"/>
+      <c r="K14" s="245"/>
+      <c r="L14" s="245"/>
+      <c r="M14" s="242"/>
+      <c r="N14" s="244"/>
     </row>
     <row r="15" spans="1:14" ht="18" customHeight="1">
       <c r="A15" s="36" t="s">
@@ -44043,10 +44048,10 @@
       <c r="H15" s="31"/>
       <c r="I15" s="31"/>
       <c r="J15" s="31"/>
-      <c r="K15" s="265"/>
-      <c r="L15" s="265"/>
-      <c r="M15" s="262"/>
-      <c r="N15" s="266"/>
+      <c r="K15" s="246"/>
+      <c r="L15" s="246"/>
+      <c r="M15" s="245"/>
+      <c r="N15" s="247"/>
     </row>
     <row r="16" spans="1:14" ht="18" customHeight="1">
       <c r="A16" s="36" t="s">
@@ -44086,111 +44091,111 @@
       <c r="N17" s="15"/>
     </row>
     <row r="18" spans="1:14" ht="18" customHeight="1">
-      <c r="A18" s="232" t="s">
+      <c r="A18" s="271" t="s">
         <v>7</v>
       </c>
-      <c r="B18" s="234" t="s">
+      <c r="B18" s="273" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="234" t="s">
+      <c r="C18" s="273" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="234" t="s">
+      <c r="D18" s="273" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="234" t="s">
+      <c r="E18" s="273" t="s">
         <v>51</v>
       </c>
-      <c r="F18" s="236" t="s">
+      <c r="F18" s="275" t="s">
         <v>52</v>
       </c>
-      <c r="G18" s="234" t="s">
+      <c r="G18" s="273" t="s">
         <v>53</v>
       </c>
-      <c r="H18" s="234" t="s">
+      <c r="H18" s="273" t="s">
         <v>14</v>
       </c>
-      <c r="I18" s="236" t="s">
+      <c r="I18" s="275" t="s">
         <v>15</v>
       </c>
-      <c r="J18" s="238" t="s">
+      <c r="J18" s="277" t="s">
         <v>16</v>
       </c>
-      <c r="K18" s="253" t="s">
+      <c r="K18" s="248" t="s">
         <v>54</v>
       </c>
-      <c r="L18" s="254"/>
-      <c r="M18" s="255">
+      <c r="L18" s="249"/>
+      <c r="M18" s="250">
         <f>100*(COUNTIF(H23:H40,"&gt;5"))</f>
         <v>1700</v>
       </c>
-      <c r="N18" s="256"/>
+      <c r="N18" s="251"/>
     </row>
     <row r="19" spans="1:14" ht="18" customHeight="1">
-      <c r="A19" s="233"/>
-      <c r="B19" s="235"/>
-      <c r="C19" s="235"/>
-      <c r="D19" s="235"/>
-      <c r="E19" s="235"/>
-      <c r="F19" s="237"/>
-      <c r="G19" s="235"/>
-      <c r="H19" s="235"/>
-      <c r="I19" s="237"/>
-      <c r="J19" s="239"/>
-      <c r="K19" s="257" t="s">
+      <c r="A19" s="272"/>
+      <c r="B19" s="274"/>
+      <c r="C19" s="274"/>
+      <c r="D19" s="274"/>
+      <c r="E19" s="274"/>
+      <c r="F19" s="276"/>
+      <c r="G19" s="274"/>
+      <c r="H19" s="274"/>
+      <c r="I19" s="276"/>
+      <c r="J19" s="278"/>
+      <c r="K19" s="252" t="s">
         <v>55</v>
       </c>
-      <c r="L19" s="258"/>
-      <c r="M19" s="245">
+      <c r="L19" s="253"/>
+      <c r="M19" s="254">
         <f>SUM(H23:H40)</f>
-        <v>1362</v>
-      </c>
-      <c r="N19" s="246"/>
+        <v>1425</v>
+      </c>
+      <c r="N19" s="255"/>
     </row>
     <row r="20" spans="1:14" ht="18" customHeight="1">
-      <c r="A20" s="233"/>
-      <c r="B20" s="235"/>
-      <c r="C20" s="235"/>
-      <c r="D20" s="235"/>
-      <c r="E20" s="235"/>
-      <c r="F20" s="237"/>
-      <c r="G20" s="235"/>
-      <c r="H20" s="235"/>
-      <c r="I20" s="237"/>
-      <c r="J20" s="239"/>
-      <c r="K20" s="257" t="s">
+      <c r="A20" s="272"/>
+      <c r="B20" s="274"/>
+      <c r="C20" s="274"/>
+      <c r="D20" s="274"/>
+      <c r="E20" s="274"/>
+      <c r="F20" s="276"/>
+      <c r="G20" s="274"/>
+      <c r="H20" s="274"/>
+      <c r="I20" s="276"/>
+      <c r="J20" s="278"/>
+      <c r="K20" s="252" t="s">
         <v>56</v>
       </c>
-      <c r="L20" s="258"/>
-      <c r="M20" s="259">
+      <c r="L20" s="253"/>
+      <c r="M20" s="256">
         <f>VLOOKUP(B14,Bsheet!A2:V52,21,0)</f>
-        <v>80.529411764705884</v>
-      </c>
-      <c r="N20" s="260"/>
+        <v>83.764705882352942</v>
+      </c>
+      <c r="N20" s="257"/>
     </row>
     <row r="21" spans="1:14" ht="18" customHeight="1">
-      <c r="A21" s="233"/>
-      <c r="B21" s="235"/>
-      <c r="C21" s="235"/>
-      <c r="D21" s="235"/>
-      <c r="E21" s="235"/>
-      <c r="F21" s="237"/>
-      <c r="G21" s="235"/>
-      <c r="H21" s="235"/>
-      <c r="I21" s="237"/>
-      <c r="J21" s="240"/>
-      <c r="K21" s="247" t="s">
+      <c r="A21" s="272"/>
+      <c r="B21" s="274"/>
+      <c r="C21" s="274"/>
+      <c r="D21" s="274"/>
+      <c r="E21" s="274"/>
+      <c r="F21" s="276"/>
+      <c r="G21" s="274"/>
+      <c r="H21" s="274"/>
+      <c r="I21" s="276"/>
+      <c r="J21" s="279"/>
+      <c r="K21" s="258" t="s">
         <v>57</v>
       </c>
-      <c r="L21" s="248"/>
-      <c r="M21" s="249">
+      <c r="L21" s="259"/>
+      <c r="M21" s="260">
         <f>VLOOKUP(B14,Bsheet!A2:V52,22,0)</f>
-        <v>4</v>
-      </c>
-      <c r="N21" s="250"/>
+        <v>1</v>
+      </c>
+      <c r="N21" s="261"/>
     </row>
     <row r="22" spans="1:14" ht="18" customHeight="1">
-      <c r="A22" s="233"/>
+      <c r="A22" s="272"/>
       <c r="B22" s="29" t="s">
         <v>58</v>
       </c>
@@ -44214,12 +44219,12 @@
       </c>
       <c r="I22" s="126"/>
       <c r="J22" s="127"/>
-      <c r="K22" s="251" t="s">
+      <c r="K22" s="262" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="251"/>
-      <c r="M22" s="251"/>
-      <c r="N22" s="252"/>
+      <c r="L22" s="262"/>
+      <c r="M22" s="262"/>
+      <c r="N22" s="263"/>
     </row>
     <row r="23" spans="1:14" ht="18" customHeight="1">
       <c r="A23" s="30" t="s">
@@ -44227,15 +44232,15 @@
       </c>
       <c r="B23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:V52,3,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,4,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,5,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,6,0)</f>
@@ -44243,31 +44248,31 @@
       </c>
       <c r="F23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,7,0)</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,8,0)</f>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:K52,9,0)</f>
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I23" s="28">
         <f>VLOOKUP(B14,Scoresheet!A3:K52,10,0)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J23" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!A3:K52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K23" s="244" t="str">
+      <c r="K23" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!A3:L52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L23" s="245"/>
-      <c r="M23" s="245"/>
-      <c r="N23" s="246"/>
+      <c r="L23" s="254"/>
+      <c r="M23" s="254"/>
+      <c r="N23" s="255"/>
     </row>
     <row r="24" spans="1:14" ht="18" customHeight="1">
       <c r="A24" s="30" t="s">
@@ -44275,7 +44280,7 @@
       </c>
       <c r="B24" s="28">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,3,0)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C24" s="28">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,4,0)</f>
@@ -44291,31 +44296,31 @@
       </c>
       <c r="F24" s="28">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,7,0)</f>
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G24" s="28">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,8,0)</f>
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H24" s="28">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,9,0)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I24" s="28">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,10,0)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J24" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!M3:W52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K24" s="244" t="str">
+      <c r="K24" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!M3:X52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L24" s="245"/>
-      <c r="M24" s="245"/>
-      <c r="N24" s="246"/>
+      <c r="L24" s="254"/>
+      <c r="M24" s="254"/>
+      <c r="N24" s="255"/>
     </row>
     <row r="25" spans="1:14" ht="18" customHeight="1">
       <c r="A25" s="30" t="s">
@@ -44331,7 +44336,7 @@
       </c>
       <c r="D25" s="28">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,5,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E25" s="28">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,6,0)</f>
@@ -44339,31 +44344,31 @@
       </c>
       <c r="F25" s="28">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,7,0)</f>
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G25" s="28">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,8,0)</f>
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H25" s="28">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,9,0)</f>
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I25" s="28">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,10,0)</f>
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J25" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y3:AI52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K25" s="244" t="str">
+      <c r="K25" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!Y3:AJ52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L25" s="245"/>
-      <c r="M25" s="245"/>
-      <c r="N25" s="246"/>
+      <c r="L25" s="254"/>
+      <c r="M25" s="254"/>
+      <c r="N25" s="255"/>
     </row>
     <row r="26" spans="1:14" ht="18" customHeight="1">
       <c r="A26" s="30" t="s">
@@ -44405,13 +44410,13 @@
         <f>VLOOKUP(B14,Scoresheet!AK3:AU52,11,0)</f>
         <v/>
       </c>
-      <c r="K26" s="244" t="str">
+      <c r="K26" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!AK3:AV52,12,0)</f>
         <v/>
       </c>
-      <c r="L26" s="245"/>
-      <c r="M26" s="245"/>
-      <c r="N26" s="246"/>
+      <c r="L26" s="254"/>
+      <c r="M26" s="254"/>
+      <c r="N26" s="255"/>
     </row>
     <row r="27" spans="1:14" ht="18" customHeight="1">
       <c r="A27" s="30" t="s">
@@ -44419,11 +44424,11 @@
       </c>
       <c r="B27" s="28">
         <f>VLOOKUP(Report!B14,Scoresheet!AW3:BG52,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C27" s="28">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,4,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D27" s="28">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,5,0)</f>
@@ -44435,7 +44440,7 @@
       </c>
       <c r="F27" s="28">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,7,0)</f>
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G27" s="28">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,8,0)</f>
@@ -44443,23 +44448,23 @@
       </c>
       <c r="H27" s="28">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,9,0)</f>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="I27" s="28">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,10,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW3:BG52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K27" s="244" t="str">
+      <c r="K27" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!AW3:BH52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L27" s="245"/>
-      <c r="M27" s="245"/>
-      <c r="N27" s="246"/>
+      <c r="L27" s="254"/>
+      <c r="M27" s="254"/>
+      <c r="N27" s="255"/>
     </row>
     <row r="28" spans="1:14" ht="18" customHeight="1">
       <c r="A28" s="30" t="s">
@@ -44467,47 +44472,47 @@
       </c>
       <c r="B28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,3,0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,4,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,5,0)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,6,0)</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,7,0)</f>
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="G28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,8,0)</f>
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,9,0)</f>
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="I28" s="28">
         <f>VLOOKUP(B14,Scoresheet!BI3:BS52,10,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J28" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI3:BU52,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K28" s="244" t="str">
+        <v>A</v>
+      </c>
+      <c r="K28" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!BI3:BT52,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L28" s="245"/>
-      <c r="M28" s="245"/>
-      <c r="N28" s="246"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L28" s="254"/>
+      <c r="M28" s="254"/>
+      <c r="N28" s="255"/>
     </row>
     <row r="29" spans="1:14" ht="18" customHeight="1">
       <c r="A29" s="30" t="s">
@@ -44515,15 +44520,15 @@
       </c>
       <c r="B29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,3,0)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,4,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,5,0)</f>
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,6,0)</f>
@@ -44531,31 +44536,31 @@
       </c>
       <c r="F29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,7,0)</f>
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,8,0)</f>
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="H29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,9,0)</f>
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="I29" s="28">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,10,0)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J29" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU3:CE52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K29" s="244" t="str">
+      <c r="K29" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!BU3:CF52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L29" s="245"/>
-      <c r="M29" s="245"/>
-      <c r="N29" s="246"/>
+      <c r="L29" s="254"/>
+      <c r="M29" s="254"/>
+      <c r="N29" s="255"/>
     </row>
     <row r="30" spans="1:14" ht="18" customHeight="1">
       <c r="A30" s="30" t="s">
@@ -44567,11 +44572,11 @@
       </c>
       <c r="C30" s="28">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,4,0)</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="28">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,5,0)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E30" s="28">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,6,0)</f>
@@ -44583,27 +44588,27 @@
       </c>
       <c r="G30" s="28">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,8,0)</f>
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H30" s="28">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,9,0)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I30" s="28">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,10,0)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG3:CQ52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K30" s="244" t="str">
+      <c r="K30" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!CG3:CR52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L30" s="245"/>
-      <c r="M30" s="245"/>
-      <c r="N30" s="246"/>
+      <c r="L30" s="254"/>
+      <c r="M30" s="254"/>
+      <c r="N30" s="255"/>
     </row>
     <row r="31" spans="1:14" ht="18" customHeight="1">
       <c r="A31" s="30" t="s">
@@ -44615,43 +44620,43 @@
       </c>
       <c r="C31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,4,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,5,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,6,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,7,0)</f>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,8,0)</f>
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="H31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,9,0)</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I31" s="28">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,10,0)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J31" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS3:DC52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K31" s="244" t="str">
+      <c r="K31" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!CS3:DD52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L31" s="245"/>
-      <c r="M31" s="245"/>
-      <c r="N31" s="246"/>
+      <c r="L31" s="254"/>
+      <c r="M31" s="254"/>
+      <c r="N31" s="255"/>
     </row>
     <row r="32" spans="1:14" ht="18" customHeight="1">
       <c r="A32" s="30" t="s">
@@ -44659,15 +44664,15 @@
       </c>
       <c r="B32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,4,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,5,0)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,6,0)</f>
@@ -44675,31 +44680,31 @@
       </c>
       <c r="F32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,7,0)</f>
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="G32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,8,0)</f>
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,9,0)</f>
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="I32" s="28">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,10,0)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J32" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE3:DO52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K32" s="244" t="str">
+      <c r="K32" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!DE3:DP52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L32" s="245"/>
-      <c r="M32" s="245"/>
-      <c r="N32" s="246"/>
+      <c r="L32" s="254"/>
+      <c r="M32" s="254"/>
+      <c r="N32" s="255"/>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1">
       <c r="A33" s="30" t="s">
@@ -44707,7 +44712,7 @@
       </c>
       <c r="B33" s="28">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,3,0)</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" s="28">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,4,0)</f>
@@ -44723,31 +44728,31 @@
       </c>
       <c r="F33" s="28">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,7,0)</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G33" s="28">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,8,0)</f>
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H33" s="28">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,9,0)</f>
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="I33" s="28">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,10,0)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J33" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EA52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K33" s="244" t="str">
+      <c r="K33" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!DQ3:EB52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L33" s="245"/>
-      <c r="M33" s="245"/>
-      <c r="N33" s="246"/>
+      <c r="L33" s="254"/>
+      <c r="M33" s="254"/>
+      <c r="N33" s="255"/>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1">
       <c r="A34" s="30" t="s">
@@ -44755,7 +44760,7 @@
       </c>
       <c r="B34" s="28">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,3,0)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C34" s="28">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,4,0)</f>
@@ -44771,31 +44776,31 @@
       </c>
       <c r="F34" s="28">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,7,0)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G34" s="28">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,8,0)</f>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H34" s="28">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,9,0)</f>
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I34" s="28">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,10,0)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J34" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC3:EM52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K34" s="244" t="str">
+      <c r="K34" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!EC3:EN52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L34" s="245"/>
-      <c r="M34" s="245"/>
-      <c r="N34" s="246"/>
+      <c r="L34" s="254"/>
+      <c r="M34" s="254"/>
+      <c r="N34" s="255"/>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1">
       <c r="A35" s="30" t="s">
@@ -44803,11 +44808,11 @@
       </c>
       <c r="B35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,3,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,4,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,5,0)</f>
@@ -44819,31 +44824,31 @@
       </c>
       <c r="F35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,7,0)</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:FA52,8,0)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,9,0)</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I35" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,10,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J35" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K35" s="244" t="str">
+        <v>A</v>
+      </c>
+      <c r="K35" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EZ52,12,0)</f>
-        <v>Credit</v>
-      </c>
-      <c r="L35" s="245"/>
-      <c r="M35" s="245"/>
-      <c r="N35" s="246"/>
+        <v>Excellent</v>
+      </c>
+      <c r="L35" s="254"/>
+      <c r="M35" s="254"/>
+      <c r="N35" s="255"/>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1">
       <c r="A36" s="30" t="s">
@@ -44855,7 +44860,7 @@
       </c>
       <c r="C36" s="28">
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,4,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D36" s="28">
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,5,0)</f>
@@ -44867,31 +44872,31 @@
       </c>
       <c r="F36" s="28">
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,7,0)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G36" s="28">
         <f>VLOOKUP(B14,Scoresheet!FA3:FL52,8,0)</f>
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H36" s="28">
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,9,0)</f>
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I36" s="28">
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,10,0)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J36" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA3:FK52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K36" s="244" t="str">
+      <c r="K36" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!FA3:FL52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L36" s="245"/>
-      <c r="M36" s="245"/>
-      <c r="N36" s="246"/>
+      <c r="L36" s="254"/>
+      <c r="M36" s="254"/>
+      <c r="N36" s="255"/>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1">
       <c r="A37" s="30" t="s">
@@ -44899,11 +44904,11 @@
       </c>
       <c r="B37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,3,0)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,4,0)</f>
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,5,0)</f>
@@ -44915,31 +44920,31 @@
       </c>
       <c r="F37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,7,0)</f>
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,8,0)</f>
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="H37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,9,0)</f>
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="I37" s="28">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,10,0)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J37" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!EO3:EY52,11,0)</f>
-        <v>C</v>
-      </c>
-      <c r="K37" s="244" t="str">
+        <v>A</v>
+      </c>
+      <c r="K37" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!FM3:FX52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L37" s="245"/>
-      <c r="M37" s="245"/>
-      <c r="N37" s="246"/>
+      <c r="L37" s="254"/>
+      <c r="M37" s="254"/>
+      <c r="N37" s="255"/>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1">
       <c r="A38" s="30" t="s">
@@ -44947,15 +44952,15 @@
       </c>
       <c r="B38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,3,0)</f>
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,4,0)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,5,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,6,0)</f>
@@ -44963,31 +44968,31 @@
       </c>
       <c r="F38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,7,0)</f>
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,8,0)</f>
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="H38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,9,0)</f>
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="I38" s="28">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,10,0)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J38" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY3:GI52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K38" s="244" t="str">
+      <c r="K38" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!FY3:GJ52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L38" s="245"/>
-      <c r="M38" s="245"/>
-      <c r="N38" s="246"/>
+      <c r="L38" s="254"/>
+      <c r="M38" s="254"/>
+      <c r="N38" s="255"/>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1">
       <c r="A39" s="30" t="s">
@@ -44999,7 +45004,7 @@
       </c>
       <c r="C39" s="28">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,4,0)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" s="28">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,5,0)</f>
@@ -45011,31 +45016,31 @@
       </c>
       <c r="F39" s="28">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,7,0)</f>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G39" s="28">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,8,0)</f>
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H39" s="28">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,9,0)</f>
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I39" s="28">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,10,0)</f>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J39" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK3:GV52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K39" s="244" t="str">
+      <c r="K39" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!GK3:GW52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L39" s="245"/>
-      <c r="M39" s="245"/>
-      <c r="N39" s="246"/>
+      <c r="L39" s="254"/>
+      <c r="M39" s="254"/>
+      <c r="N39" s="255"/>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1">
       <c r="A40" s="30" t="s">
@@ -45043,7 +45048,7 @@
       </c>
       <c r="B40" s="28">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,3,0)</f>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40" s="28">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,4,0)</f>
@@ -45059,7 +45064,7 @@
       </c>
       <c r="F40" s="28">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,7,0)</f>
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G40" s="28">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,8,0)</f>
@@ -45067,23 +45072,23 @@
       </c>
       <c r="H40" s="28">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,9,0)</f>
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="I40" s="28">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,10,0)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J40" s="28" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,11,0)</f>
         <v>A</v>
       </c>
-      <c r="K40" s="244" t="str">
+      <c r="K40" s="264" t="str">
         <f>VLOOKUP(B14,Scoresheet!GW3:HH52,12,0)</f>
         <v>Excellent</v>
       </c>
-      <c r="L40" s="245"/>
-      <c r="M40" s="245"/>
-      <c r="N40" s="246"/>
+      <c r="L40" s="254"/>
+      <c r="M40" s="254"/>
+      <c r="N40" s="255"/>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1">
       <c r="A41" s="23"/>
@@ -45107,20 +45112,20 @@
       </c>
       <c r="B42" s="38"/>
       <c r="C42" s="4"/>
-      <c r="D42" s="242" t="s">
+      <c r="D42" s="265" t="s">
         <v>71</v>
       </c>
-      <c r="E42" s="242"/>
+      <c r="E42" s="265"/>
       <c r="F42" s="40"/>
       <c r="G42" s="41"/>
-      <c r="H42" s="243" t="s">
+      <c r="H42" s="266" t="s">
         <v>72</v>
       </c>
-      <c r="I42" s="243"/>
-      <c r="J42" s="243"/>
-      <c r="K42" s="243"/>
-      <c r="L42" s="243"/>
-      <c r="M42" s="243"/>
+      <c r="I42" s="266"/>
+      <c r="J42" s="266"/>
+      <c r="K42" s="266"/>
+      <c r="L42" s="266"/>
+      <c r="M42" s="266"/>
       <c r="N42" s="42"/>
       <c r="O42" s="18"/>
     </row>
@@ -45133,23 +45138,23 @@
         <v>5</v>
       </c>
       <c r="C43" s="4"/>
-      <c r="D43" s="242" t="s">
+      <c r="D43" s="265" t="s">
         <v>30</v>
       </c>
-      <c r="E43" s="242"/>
+      <c r="E43" s="265"/>
       <c r="F43" s="40">
         <f>VLOOKUP(B14,Skills!A2:H51,3,0)</f>
         <v>5</v>
       </c>
       <c r="G43" s="41"/>
-      <c r="H43" s="243" t="s">
+      <c r="H43" s="266" t="s">
         <v>73</v>
       </c>
-      <c r="I43" s="243"/>
-      <c r="J43" s="243"/>
-      <c r="K43" s="243"/>
-      <c r="L43" s="243"/>
-      <c r="M43" s="243"/>
+      <c r="I43" s="266"/>
+      <c r="J43" s="266"/>
+      <c r="K43" s="266"/>
+      <c r="L43" s="266"/>
+      <c r="M43" s="266"/>
       <c r="N43" s="42"/>
       <c r="O43" s="18"/>
     </row>
@@ -45162,23 +45167,23 @@
         <v>5</v>
       </c>
       <c r="C44" s="4"/>
-      <c r="D44" s="242" t="s">
+      <c r="D44" s="265" t="s">
         <v>31</v>
       </c>
-      <c r="E44" s="242"/>
+      <c r="E44" s="265"/>
       <c r="F44" s="40">
         <f>VLOOKUP(B14,Skills!A2:H51,4,0)</f>
         <v>5</v>
       </c>
       <c r="G44" s="41"/>
-      <c r="H44" s="243" t="s">
+      <c r="H44" s="266" t="s">
         <v>74</v>
       </c>
-      <c r="I44" s="243"/>
-      <c r="J44" s="243"/>
-      <c r="K44" s="243"/>
-      <c r="L44" s="243"/>
-      <c r="M44" s="243"/>
+      <c r="I44" s="266"/>
+      <c r="J44" s="266"/>
+      <c r="K44" s="266"/>
+      <c r="L44" s="266"/>
+      <c r="M44" s="266"/>
       <c r="N44" s="42"/>
       <c r="O44" s="18"/>
     </row>
@@ -45191,23 +45196,23 @@
         <v>5</v>
       </c>
       <c r="C45" s="4"/>
-      <c r="D45" s="242" t="s">
+      <c r="D45" s="265" t="s">
         <v>32</v>
       </c>
-      <c r="E45" s="242"/>
+      <c r="E45" s="265"/>
       <c r="F45" s="40">
         <f>VLOOKUP(B14,Skills!A2:H51,5,0)</f>
         <v>5</v>
       </c>
       <c r="G45" s="41"/>
-      <c r="H45" s="243" t="s">
+      <c r="H45" s="266" t="s">
         <v>75</v>
       </c>
-      <c r="I45" s="243"/>
-      <c r="J45" s="243"/>
-      <c r="K45" s="243"/>
-      <c r="L45" s="243"/>
-      <c r="M45" s="243"/>
+      <c r="I45" s="266"/>
+      <c r="J45" s="266"/>
+      <c r="K45" s="266"/>
+      <c r="L45" s="266"/>
+      <c r="M45" s="266"/>
       <c r="N45" s="42"/>
       <c r="O45" s="18"/>
     </row>
@@ -45220,23 +45225,23 @@
         <v>5</v>
       </c>
       <c r="C46" s="4"/>
-      <c r="D46" s="242" t="s">
+      <c r="D46" s="265" t="s">
         <v>33</v>
       </c>
-      <c r="E46" s="242"/>
+      <c r="E46" s="265"/>
       <c r="F46" s="40">
         <f>VLOOKUP(B14,Skills!A2:H51,6,0)</f>
         <v>5</v>
       </c>
       <c r="G46" s="41"/>
-      <c r="H46" s="243" t="s">
+      <c r="H46" s="266" t="s">
         <v>76</v>
       </c>
-      <c r="I46" s="243"/>
-      <c r="J46" s="243"/>
-      <c r="K46" s="243"/>
-      <c r="L46" s="243"/>
-      <c r="M46" s="243"/>
+      <c r="I46" s="266"/>
+      <c r="J46" s="266"/>
+      <c r="K46" s="266"/>
+      <c r="L46" s="266"/>
+      <c r="M46" s="266"/>
       <c r="N46" s="42"/>
       <c r="O46" s="18"/>
     </row>
@@ -45249,23 +45254,23 @@
         <v>5</v>
       </c>
       <c r="C47" s="4"/>
-      <c r="D47" s="242" t="s">
+      <c r="D47" s="265" t="s">
         <v>34</v>
       </c>
-      <c r="E47" s="242"/>
+      <c r="E47" s="265"/>
       <c r="F47" s="40">
         <f>VLOOKUP(B16,Skills!A2:H51,7,0)</f>
         <v>0</v>
       </c>
       <c r="G47" s="41"/>
-      <c r="H47" s="243" t="s">
+      <c r="H47" s="266" t="s">
         <v>77</v>
       </c>
-      <c r="I47" s="243"/>
-      <c r="J47" s="243"/>
-      <c r="K47" s="243"/>
-      <c r="L47" s="243"/>
-      <c r="M47" s="243"/>
+      <c r="I47" s="266"/>
+      <c r="J47" s="266"/>
+      <c r="K47" s="266"/>
+      <c r="L47" s="266"/>
+      <c r="M47" s="266"/>
       <c r="N47" s="42"/>
       <c r="O47" s="18"/>
     </row>
@@ -45370,11 +45375,11 @@
       <c r="O52" s="18"/>
     </row>
     <row r="53" spans="1:20" ht="18" customHeight="1">
-      <c r="A53" s="229" t="s">
+      <c r="A53" s="267" t="s">
         <v>78</v>
       </c>
-      <c r="B53" s="230"/>
-      <c r="C53" s="230"/>
+      <c r="B53" s="268"/>
+      <c r="C53" s="268"/>
       <c r="D53" s="18" t="s">
         <v>79</v>
       </c>
@@ -45392,16 +45397,16 @@
       <c r="M53" s="18"/>
       <c r="N53" s="16"/>
       <c r="O53" s="18"/>
-      <c r="R53" s="231"/>
-      <c r="S53" s="231"/>
-      <c r="T53" s="231"/>
+      <c r="R53" s="270"/>
+      <c r="S53" s="270"/>
+      <c r="T53" s="270"/>
     </row>
     <row r="54" spans="1:20" ht="18" customHeight="1">
-      <c r="A54" s="229" t="s">
+      <c r="A54" s="267" t="s">
         <v>80</v>
       </c>
-      <c r="B54" s="230"/>
-      <c r="C54" s="230"/>
+      <c r="B54" s="268"/>
+      <c r="C54" s="268"/>
       <c r="D54" s="18" t="s">
         <v>79</v>
       </c>
@@ -45416,43 +45421,43 @@
       <c r="M54" s="18"/>
       <c r="N54" s="16"/>
       <c r="O54" s="18"/>
-      <c r="R54" s="231"/>
-      <c r="S54" s="231"/>
-      <c r="T54" s="231"/>
+      <c r="R54" s="270"/>
+      <c r="S54" s="270"/>
+      <c r="T54" s="270"/>
     </row>
     <row r="55" spans="1:20" ht="18" customHeight="1">
-      <c r="A55" s="229" t="s">
+      <c r="A55" s="267" t="s">
         <v>81</v>
       </c>
-      <c r="B55" s="230"/>
-      <c r="C55" s="230"/>
+      <c r="B55" s="268"/>
+      <c r="C55" s="268"/>
       <c r="D55" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="E55" s="241" t="str">
+      <c r="E55" s="269" t="str">
         <f>VLOOKUP(B14,Comments!A2:C51,3,0)</f>
         <v>Nil</v>
       </c>
-      <c r="F55" s="241"/>
-      <c r="G55" s="241"/>
-      <c r="H55" s="241"/>
-      <c r="I55" s="241"/>
-      <c r="J55" s="241"/>
+      <c r="F55" s="269"/>
+      <c r="G55" s="269"/>
+      <c r="H55" s="269"/>
+      <c r="I55" s="269"/>
+      <c r="J55" s="269"/>
       <c r="K55" s="18"/>
       <c r="L55" s="18"/>
       <c r="M55" s="18"/>
       <c r="N55" s="16"/>
       <c r="O55" s="18"/>
-      <c r="R55" s="231"/>
-      <c r="S55" s="231"/>
-      <c r="T55" s="231"/>
+      <c r="R55" s="270"/>
+      <c r="S55" s="270"/>
+      <c r="T55" s="270"/>
     </row>
     <row r="56" spans="1:20" ht="18" customHeight="1">
-      <c r="A56" s="229" t="s">
+      <c r="A56" s="267" t="s">
         <v>82</v>
       </c>
-      <c r="B56" s="230"/>
-      <c r="C56" s="230"/>
+      <c r="B56" s="268"/>
+      <c r="C56" s="268"/>
       <c r="D56" s="18" t="s">
         <v>79</v>
       </c>
@@ -45470,9 +45475,9 @@
       <c r="M56" s="18"/>
       <c r="N56" s="16"/>
       <c r="O56" s="18"/>
-      <c r="R56" s="231"/>
-      <c r="S56" s="231"/>
-      <c r="T56" s="231"/>
+      <c r="R56" s="270"/>
+      <c r="S56" s="270"/>
+      <c r="T56" s="270"/>
     </row>
     <row r="57" spans="1:20" ht="18" customHeight="1" thickBot="1">
       <c r="A57" s="25"/>
@@ -45509,65 +45514,6 @@
   </protectedRanges>
   <dataConsolidate/>
   <mergeCells count="75">
-    <mergeCell ref="B10:G10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:G11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="B12:G12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B13:G13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="K22:N22"/>
-    <mergeCell ref="K23:N23"/>
-    <mergeCell ref="K24:N24"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="K27:N27"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="K30:N30"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="K37:N37"/>
-    <mergeCell ref="K38:N38"/>
-    <mergeCell ref="K39:N39"/>
-    <mergeCell ref="K40:N40"/>
-    <mergeCell ref="K32:N32"/>
-    <mergeCell ref="K33:N33"/>
-    <mergeCell ref="K34:N34"/>
-    <mergeCell ref="K35:N35"/>
-    <mergeCell ref="K36:N36"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="H42:M42"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H44:M44"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="R55:T55"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="H45:M45"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="H46:M46"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="H47:M47"/>
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="R56:T56"/>
     <mergeCell ref="A18:A22"/>
@@ -45584,6 +45530,65 @@
     <mergeCell ref="R53:T53"/>
     <mergeCell ref="A54:C54"/>
     <mergeCell ref="R54:T54"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="R55:T55"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="H45:M45"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="H46:M46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="H47:M47"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H42:M42"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="H44:M44"/>
+    <mergeCell ref="K40:N40"/>
+    <mergeCell ref="K32:N32"/>
+    <mergeCell ref="K33:N33"/>
+    <mergeCell ref="K34:N34"/>
+    <mergeCell ref="K35:N35"/>
+    <mergeCell ref="K36:N36"/>
+    <mergeCell ref="K30:N30"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="K37:N37"/>
+    <mergeCell ref="K38:N38"/>
+    <mergeCell ref="K39:N39"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="K27:N27"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="K22:N22"/>
+    <mergeCell ref="K23:N23"/>
+    <mergeCell ref="K24:N24"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B12:G12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B13:G13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="B10:G10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M11:N11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.25" top="0.25" bottom="0" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" r:id="rId1"/>
@@ -45618,1586 +45623,1586 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="147" customFormat="1" ht="23.25" customHeight="1">
-      <c r="A1" s="288" t="s">
+      <c r="A1" s="285" t="s">
         <v>221</v>
       </c>
-      <c r="B1" s="289"/>
-      <c r="C1" s="289"/>
-      <c r="D1" s="289"/>
-      <c r="E1" s="289"/>
-      <c r="F1" s="289"/>
-      <c r="G1" s="289"/>
-      <c r="H1" s="289"/>
-      <c r="I1" s="289"/>
-      <c r="J1" s="289"/>
-      <c r="K1" s="289"/>
-      <c r="L1" s="290"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
+      <c r="J1" s="286"/>
+      <c r="K1" s="286"/>
+      <c r="L1" s="287"/>
     </row>
     <row r="2" spans="1:12" s="148" customFormat="1">
-      <c r="A2" s="268" t="s">
+      <c r="A2" s="213" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="269"/>
-      <c r="C2" s="270"/>
-      <c r="D2" s="270"/>
-      <c r="E2" s="270"/>
-      <c r="F2" s="270"/>
-      <c r="G2" s="270"/>
-      <c r="H2" s="270"/>
-      <c r="I2" s="270"/>
-      <c r="J2" s="270"/>
-      <c r="K2" s="270"/>
-      <c r="L2" s="271"/>
+      <c r="B2" s="288"/>
+      <c r="C2" s="289"/>
+      <c r="D2" s="289"/>
+      <c r="E2" s="289"/>
+      <c r="F2" s="289"/>
+      <c r="G2" s="289"/>
+      <c r="H2" s="289"/>
+      <c r="I2" s="289"/>
+      <c r="J2" s="289"/>
+      <c r="K2" s="289"/>
+      <c r="L2" s="290"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="268" t="s">
+      <c r="A3" s="213" t="s">
         <v>222</v>
       </c>
-      <c r="B3" s="272" t="s">
+      <c r="B3" s="280" t="s">
         <v>233</v>
       </c>
-      <c r="C3" s="272"/>
-      <c r="D3" s="272"/>
-      <c r="E3" s="272"/>
-      <c r="F3" s="272"/>
-      <c r="G3" s="272"/>
-      <c r="H3" s="272"/>
-      <c r="I3" s="272"/>
-      <c r="J3" s="272"/>
-      <c r="K3" s="272"/>
-      <c r="L3" s="273"/>
+      <c r="C3" s="280"/>
+      <c r="D3" s="280"/>
+      <c r="E3" s="280"/>
+      <c r="F3" s="280"/>
+      <c r="G3" s="280"/>
+      <c r="H3" s="280"/>
+      <c r="I3" s="280"/>
+      <c r="J3" s="280"/>
+      <c r="K3" s="280"/>
+      <c r="L3" s="281"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="274" t="s">
+      <c r="A4" s="282" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="275"/>
-      <c r="C4" s="275"/>
-      <c r="D4" s="275"/>
-      <c r="E4" s="275"/>
-      <c r="F4" s="275"/>
-      <c r="G4" s="275"/>
-      <c r="H4" s="275"/>
-      <c r="I4" s="275"/>
-      <c r="J4" s="275"/>
-      <c r="K4" s="275"/>
-      <c r="L4" s="276"/>
-    </row>
-    <row r="5" spans="1:12" ht="97.5">
-      <c r="A5" s="277" t="s">
+      <c r="B4" s="283"/>
+      <c r="C4" s="283"/>
+      <c r="D4" s="283"/>
+      <c r="E4" s="283"/>
+      <c r="F4" s="283"/>
+      <c r="G4" s="283"/>
+      <c r="H4" s="283"/>
+      <c r="I4" s="283"/>
+      <c r="J4" s="283"/>
+      <c r="K4" s="283"/>
+      <c r="L4" s="284"/>
+    </row>
+    <row r="5" spans="1:12" ht="96.75">
+      <c r="A5" s="214" t="s">
         <v>224</v>
       </c>
-      <c r="B5" s="278" t="s">
+      <c r="B5" s="215" t="s">
         <v>225</v>
       </c>
-      <c r="C5" s="279" t="s">
+      <c r="C5" s="216" t="s">
         <v>226</v>
       </c>
-      <c r="D5" s="279" t="s">
+      <c r="D5" s="216" t="s">
         <v>227</v>
       </c>
-      <c r="E5" s="279" t="s">
+      <c r="E5" s="216" t="s">
         <v>228</v>
       </c>
-      <c r="F5" s="279" t="s">
+      <c r="F5" s="216" t="s">
         <v>229</v>
       </c>
-      <c r="G5" s="279" t="s">
+      <c r="G5" s="216" t="s">
         <v>230</v>
       </c>
-      <c r="H5" s="279" t="s">
+      <c r="H5" s="216" t="s">
         <v>231</v>
       </c>
-      <c r="I5" s="279" t="s">
+      <c r="I5" s="216" t="s">
         <v>232</v>
       </c>
-      <c r="J5" s="279" t="s">
+      <c r="J5" s="216" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="279" t="s">
+      <c r="K5" s="216" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="280"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="281">
+      <c r="A6" s="218">
         <v>1</v>
       </c>
-      <c r="B6" s="267" t="s">
+      <c r="B6" s="212" t="s">
         <v>102</v>
       </c>
-      <c r="C6" s="282"/>
-      <c r="D6" s="282"/>
-      <c r="E6" s="282"/>
-      <c r="F6" s="282"/>
-      <c r="G6" s="282">
+      <c r="C6" s="219"/>
+      <c r="D6" s="219"/>
+      <c r="E6" s="219"/>
+      <c r="F6" s="219"/>
+      <c r="G6" s="219">
         <f>SUM(C6:F6)</f>
         <v>0</v>
       </c>
-      <c r="H6" s="282"/>
-      <c r="I6" s="282">
+      <c r="H6" s="219"/>
+      <c r="I6" s="219">
         <f>G6+H6</f>
         <v>0</v>
       </c>
-      <c r="J6" s="282" t="str">
+      <c r="J6" s="219" t="str">
         <f>IF(I6&lt;10,"",RANK(I6,I$6:I$55))</f>
         <v/>
       </c>
-      <c r="K6" s="282" t="str">
+      <c r="K6" s="219" t="str">
         <f>IF(I6&gt;=75,"A",IF(I6&gt;=70,"B2",IF(I6&gt;=50,"C",IF(I6&gt;=45,"D",IF(I6&gt;=40,"E",IF(I6&gt;=6,"F",IF(I6&lt;5,"")))))))</f>
         <v/>
       </c>
-      <c r="L6" s="283"/>
+      <c r="L6" s="220"/>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="281">
+      <c r="A7" s="218">
         <v>2</v>
       </c>
-      <c r="B7" s="267" t="s">
+      <c r="B7" s="212" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="282"/>
-      <c r="D7" s="282"/>
-      <c r="E7" s="282"/>
-      <c r="F7" s="282"/>
-      <c r="G7" s="282">
+      <c r="C7" s="219"/>
+      <c r="D7" s="219"/>
+      <c r="E7" s="219"/>
+      <c r="F7" s="219"/>
+      <c r="G7" s="219">
         <f t="shared" ref="G7:G55" si="0">SUM(C7:F7)</f>
         <v>0</v>
       </c>
-      <c r="H7" s="282"/>
-      <c r="I7" s="282">
+      <c r="H7" s="219"/>
+      <c r="I7" s="219">
         <f t="shared" ref="I7:I55" si="1">G7+H7</f>
         <v>0</v>
       </c>
-      <c r="J7" s="282" t="str">
+      <c r="J7" s="219" t="str">
         <f t="shared" ref="J7:J55" si="2">IF(I7&lt;10,"",RANK(I7,I$6:I$55))</f>
         <v/>
       </c>
-      <c r="K7" s="282" t="str">
+      <c r="K7" s="219" t="str">
         <f t="shared" ref="K7:K55" si="3">IF(I7&gt;=75,"A",IF(I7&gt;=70,"B2",IF(I7&gt;=50,"C",IF(I7&gt;=45,"D",IF(I7&gt;=40,"E",IF(I7&gt;=6,"F",IF(I7&lt;5,"")))))))</f>
         <v/>
       </c>
-      <c r="L7" s="283"/>
+      <c r="L7" s="220"/>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="281">
+      <c r="A8" s="218">
         <v>3</v>
       </c>
-      <c r="B8" s="267" t="s">
+      <c r="B8" s="212" t="s">
         <v>104</v>
       </c>
-      <c r="C8" s="282"/>
-      <c r="D8" s="282"/>
-      <c r="E8" s="282"/>
-      <c r="F8" s="282"/>
-      <c r="G8" s="282">
+      <c r="C8" s="219"/>
+      <c r="D8" s="219"/>
+      <c r="E8" s="219"/>
+      <c r="F8" s="219"/>
+      <c r="G8" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H8" s="282"/>
-      <c r="I8" s="282">
+      <c r="H8" s="219"/>
+      <c r="I8" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="282" t="str">
+      <c r="J8" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K8" s="282" t="str">
+      <c r="K8" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L8" s="283"/>
+      <c r="L8" s="220"/>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="281">
+      <c r="A9" s="218">
         <v>4</v>
       </c>
-      <c r="B9" s="267" t="s">
+      <c r="B9" s="212" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="282"/>
-      <c r="D9" s="282"/>
-      <c r="E9" s="282"/>
-      <c r="F9" s="282"/>
-      <c r="G9" s="282">
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="G9" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H9" s="282"/>
-      <c r="I9" s="282">
+      <c r="H9" s="219"/>
+      <c r="I9" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J9" s="282" t="str">
+      <c r="J9" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K9" s="282" t="str">
+      <c r="K9" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L9" s="283"/>
+      <c r="L9" s="220"/>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="281">
-        <v>5</v>
-      </c>
-      <c r="B10" s="267" t="s">
+      <c r="A10" s="218">
+        <v>5</v>
+      </c>
+      <c r="B10" s="212" t="s">
         <v>106</v>
       </c>
-      <c r="C10" s="282"/>
-      <c r="D10" s="282"/>
-      <c r="E10" s="282"/>
-      <c r="F10" s="282"/>
-      <c r="G10" s="282">
+      <c r="C10" s="219"/>
+      <c r="D10" s="219"/>
+      <c r="E10" s="219"/>
+      <c r="F10" s="219"/>
+      <c r="G10" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="282"/>
-      <c r="I10" s="282">
+      <c r="H10" s="219"/>
+      <c r="I10" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J10" s="282" t="str">
+      <c r="J10" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K10" s="282" t="str">
+      <c r="K10" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L10" s="283"/>
+      <c r="L10" s="220"/>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="281">
+      <c r="A11" s="218">
         <v>6</v>
       </c>
-      <c r="B11" s="267" t="s">
+      <c r="B11" s="212" t="s">
         <v>107</v>
       </c>
-      <c r="C11" s="282"/>
-      <c r="D11" s="282"/>
-      <c r="E11" s="282"/>
-      <c r="F11" s="282"/>
-      <c r="G11" s="282">
+      <c r="C11" s="219"/>
+      <c r="D11" s="219"/>
+      <c r="E11" s="219"/>
+      <c r="F11" s="219"/>
+      <c r="G11" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="282"/>
-      <c r="I11" s="282">
+      <c r="H11" s="219"/>
+      <c r="I11" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J11" s="282" t="str">
+      <c r="J11" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K11" s="282" t="str">
+      <c r="K11" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L11" s="283"/>
+      <c r="L11" s="220"/>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="281">
+      <c r="A12" s="218">
         <v>7</v>
       </c>
-      <c r="B12" s="267" t="s">
+      <c r="B12" s="212" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="282"/>
-      <c r="D12" s="282"/>
-      <c r="E12" s="282"/>
-      <c r="F12" s="282"/>
-      <c r="G12" s="282">
+      <c r="C12" s="219"/>
+      <c r="D12" s="219"/>
+      <c r="E12" s="219"/>
+      <c r="F12" s="219"/>
+      <c r="G12" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="282"/>
-      <c r="I12" s="282">
+      <c r="H12" s="219"/>
+      <c r="I12" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J12" s="282" t="str">
+      <c r="J12" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K12" s="282" t="str">
+      <c r="K12" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L12" s="283"/>
+      <c r="L12" s="220"/>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="281">
+      <c r="A13" s="218">
         <v>8</v>
       </c>
-      <c r="B13" s="267" t="s">
+      <c r="B13" s="212" t="s">
         <v>110</v>
       </c>
-      <c r="C13" s="282"/>
-      <c r="D13" s="282"/>
-      <c r="E13" s="282"/>
-      <c r="F13" s="282"/>
-      <c r="G13" s="282">
+      <c r="C13" s="219"/>
+      <c r="D13" s="219"/>
+      <c r="E13" s="219"/>
+      <c r="F13" s="219"/>
+      <c r="G13" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="282"/>
-      <c r="I13" s="282">
+      <c r="H13" s="219"/>
+      <c r="I13" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J13" s="282" t="str">
+      <c r="J13" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K13" s="282" t="str">
+      <c r="K13" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L13" s="283"/>
+      <c r="L13" s="220"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="281">
+      <c r="A14" s="218">
         <v>9</v>
       </c>
-      <c r="B14" s="267" t="s">
+      <c r="B14" s="212" t="s">
         <v>111</v>
       </c>
-      <c r="C14" s="282"/>
-      <c r="D14" s="282"/>
-      <c r="E14" s="282"/>
-      <c r="F14" s="282"/>
-      <c r="G14" s="282">
+      <c r="C14" s="219"/>
+      <c r="D14" s="219"/>
+      <c r="E14" s="219"/>
+      <c r="F14" s="219"/>
+      <c r="G14" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="282"/>
-      <c r="I14" s="282">
+      <c r="H14" s="219"/>
+      <c r="I14" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J14" s="282" t="str">
+      <c r="J14" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K14" s="282" t="str">
+      <c r="K14" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L14" s="283"/>
+      <c r="L14" s="220"/>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="281">
-        <v>10</v>
-      </c>
-      <c r="B15" s="267" t="s">
+      <c r="A15" s="218">
+        <v>10</v>
+      </c>
+      <c r="B15" s="212" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="282"/>
-      <c r="D15" s="282"/>
-      <c r="E15" s="282"/>
-      <c r="F15" s="282"/>
-      <c r="G15" s="282">
+      <c r="C15" s="219"/>
+      <c r="D15" s="219"/>
+      <c r="E15" s="219"/>
+      <c r="F15" s="219"/>
+      <c r="G15" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="282"/>
-      <c r="I15" s="282">
+      <c r="H15" s="219"/>
+      <c r="I15" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J15" s="282" t="str">
+      <c r="J15" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K15" s="282" t="str">
+      <c r="K15" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L15" s="283"/>
+      <c r="L15" s="220"/>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="281">
+      <c r="A16" s="218">
         <v>11</v>
       </c>
-      <c r="B16" s="267" t="s">
+      <c r="B16" s="212" t="s">
         <v>113</v>
       </c>
-      <c r="C16" s="282"/>
-      <c r="D16" s="282"/>
-      <c r="E16" s="282"/>
-      <c r="F16" s="282"/>
-      <c r="G16" s="282">
+      <c r="C16" s="219"/>
+      <c r="D16" s="219"/>
+      <c r="E16" s="219"/>
+      <c r="F16" s="219"/>
+      <c r="G16" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="282"/>
-      <c r="I16" s="282">
+      <c r="H16" s="219"/>
+      <c r="I16" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J16" s="282" t="str">
+      <c r="J16" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K16" s="282" t="str">
+      <c r="K16" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L16" s="283"/>
+      <c r="L16" s="220"/>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="281">
+      <c r="A17" s="218">
         <v>12</v>
       </c>
-      <c r="B17" s="267" t="s">
+      <c r="B17" s="212" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="282"/>
-      <c r="D17" s="282"/>
-      <c r="E17" s="282"/>
-      <c r="F17" s="282"/>
-      <c r="G17" s="282">
+      <c r="C17" s="219"/>
+      <c r="D17" s="219"/>
+      <c r="E17" s="219"/>
+      <c r="F17" s="219"/>
+      <c r="G17" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H17" s="282"/>
-      <c r="I17" s="282">
+      <c r="H17" s="219"/>
+      <c r="I17" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J17" s="282" t="str">
+      <c r="J17" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K17" s="282" t="str">
+      <c r="K17" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L17" s="283"/>
+      <c r="L17" s="220"/>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="281">
+      <c r="A18" s="218">
         <v>13</v>
       </c>
-      <c r="B18" s="267" t="s">
+      <c r="B18" s="212" t="s">
         <v>115</v>
       </c>
-      <c r="C18" s="282"/>
-      <c r="D18" s="282"/>
-      <c r="E18" s="282"/>
-      <c r="F18" s="282"/>
-      <c r="G18" s="282">
+      <c r="C18" s="219"/>
+      <c r="D18" s="219"/>
+      <c r="E18" s="219"/>
+      <c r="F18" s="219"/>
+      <c r="G18" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="282"/>
-      <c r="I18" s="282">
+      <c r="H18" s="219"/>
+      <c r="I18" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J18" s="282" t="str">
+      <c r="J18" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K18" s="282" t="str">
+      <c r="K18" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L18" s="283"/>
+      <c r="L18" s="220"/>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="281">
+      <c r="A19" s="218">
         <v>14</v>
       </c>
-      <c r="B19" s="267" t="s">
+      <c r="B19" s="212" t="s">
         <v>116</v>
       </c>
-      <c r="C19" s="282"/>
-      <c r="D19" s="282"/>
-      <c r="E19" s="282"/>
-      <c r="F19" s="282"/>
-      <c r="G19" s="282">
+      <c r="C19" s="219"/>
+      <c r="D19" s="219"/>
+      <c r="E19" s="219"/>
+      <c r="F19" s="219"/>
+      <c r="G19" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="282"/>
-      <c r="I19" s="282">
+      <c r="H19" s="219"/>
+      <c r="I19" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J19" s="282" t="str">
+      <c r="J19" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K19" s="282" t="str">
+      <c r="K19" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L19" s="283"/>
+      <c r="L19" s="220"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="281">
+      <c r="A20" s="218">
         <v>15</v>
       </c>
-      <c r="B20" s="267" t="s">
+      <c r="B20" s="212" t="s">
         <v>117</v>
       </c>
-      <c r="C20" s="282"/>
-      <c r="D20" s="282"/>
-      <c r="E20" s="282"/>
-      <c r="F20" s="282"/>
-      <c r="G20" s="282">
+      <c r="C20" s="219"/>
+      <c r="D20" s="219"/>
+      <c r="E20" s="219"/>
+      <c r="F20" s="219"/>
+      <c r="G20" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="282"/>
-      <c r="I20" s="282">
+      <c r="H20" s="219"/>
+      <c r="I20" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J20" s="282" t="str">
+      <c r="J20" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K20" s="282" t="str">
+      <c r="K20" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L20" s="283"/>
+      <c r="L20" s="220"/>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="281">
+      <c r="A21" s="218">
         <v>16</v>
       </c>
-      <c r="B21" s="267" t="s">
+      <c r="B21" s="212" t="s">
         <v>118</v>
       </c>
-      <c r="C21" s="282"/>
-      <c r="D21" s="282"/>
-      <c r="E21" s="282"/>
-      <c r="F21" s="282"/>
-      <c r="G21" s="282">
+      <c r="C21" s="219"/>
+      <c r="D21" s="219"/>
+      <c r="E21" s="219"/>
+      <c r="F21" s="219"/>
+      <c r="G21" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="282"/>
-      <c r="I21" s="282">
+      <c r="H21" s="219"/>
+      <c r="I21" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J21" s="282" t="str">
+      <c r="J21" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K21" s="282" t="str">
+      <c r="K21" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L21" s="283"/>
+      <c r="L21" s="220"/>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="281">
+      <c r="A22" s="218">
         <v>17</v>
       </c>
-      <c r="B22" s="267" t="s">
+      <c r="B22" s="212" t="s">
         <v>119</v>
       </c>
-      <c r="C22" s="282"/>
-      <c r="D22" s="282"/>
-      <c r="E22" s="282"/>
-      <c r="F22" s="282"/>
-      <c r="G22" s="282">
+      <c r="C22" s="219"/>
+      <c r="D22" s="219"/>
+      <c r="E22" s="219"/>
+      <c r="F22" s="219"/>
+      <c r="G22" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="282"/>
-      <c r="I22" s="282">
+      <c r="H22" s="219"/>
+      <c r="I22" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J22" s="282" t="str">
+      <c r="J22" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K22" s="282" t="str">
+      <c r="K22" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L22" s="283"/>
+      <c r="L22" s="220"/>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="281">
+      <c r="A23" s="218">
         <v>18</v>
       </c>
-      <c r="B23" s="267" t="s">
+      <c r="B23" s="212" t="s">
         <v>120</v>
       </c>
-      <c r="C23" s="282"/>
-      <c r="D23" s="282"/>
-      <c r="E23" s="282"/>
-      <c r="F23" s="282"/>
-      <c r="G23" s="282">
+      <c r="C23" s="219"/>
+      <c r="D23" s="219"/>
+      <c r="E23" s="219"/>
+      <c r="F23" s="219"/>
+      <c r="G23" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H23" s="282"/>
-      <c r="I23" s="282">
+      <c r="H23" s="219"/>
+      <c r="I23" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J23" s="282" t="str">
+      <c r="J23" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K23" s="282" t="str">
+      <c r="K23" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L23" s="283"/>
+      <c r="L23" s="220"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="281">
+      <c r="A24" s="218">
         <v>19</v>
       </c>
-      <c r="B24" s="267" t="s">
+      <c r="B24" s="212" t="s">
         <v>121</v>
       </c>
-      <c r="C24" s="282"/>
-      <c r="D24" s="282"/>
-      <c r="E24" s="282"/>
-      <c r="F24" s="282"/>
-      <c r="G24" s="282">
+      <c r="C24" s="219"/>
+      <c r="D24" s="219"/>
+      <c r="E24" s="219"/>
+      <c r="F24" s="219"/>
+      <c r="G24" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="282"/>
-      <c r="I24" s="282">
+      <c r="H24" s="219"/>
+      <c r="I24" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J24" s="282" t="str">
+      <c r="J24" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K24" s="282" t="str">
+      <c r="K24" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L24" s="283"/>
+      <c r="L24" s="220"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="281">
+      <c r="A25" s="218">
         <v>20</v>
       </c>
-      <c r="B25" s="267" t="s">
+      <c r="B25" s="212" t="s">
         <v>122</v>
       </c>
-      <c r="C25" s="282"/>
-      <c r="D25" s="282"/>
-      <c r="E25" s="282"/>
-      <c r="F25" s="282"/>
-      <c r="G25" s="282">
+      <c r="C25" s="219"/>
+      <c r="D25" s="219"/>
+      <c r="E25" s="219"/>
+      <c r="F25" s="219"/>
+      <c r="G25" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="282"/>
-      <c r="I25" s="282">
+      <c r="H25" s="219"/>
+      <c r="I25" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J25" s="282" t="str">
+      <c r="J25" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K25" s="282" t="str">
+      <c r="K25" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L25" s="283"/>
+      <c r="L25" s="220"/>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="281">
+      <c r="A26" s="218">
         <v>21</v>
       </c>
-      <c r="B26" s="267" t="s">
+      <c r="B26" s="212" t="s">
         <v>123</v>
       </c>
-      <c r="C26" s="282"/>
-      <c r="D26" s="282"/>
-      <c r="E26" s="282"/>
-      <c r="F26" s="282"/>
-      <c r="G26" s="282">
+      <c r="C26" s="219"/>
+      <c r="D26" s="219"/>
+      <c r="E26" s="219"/>
+      <c r="F26" s="219"/>
+      <c r="G26" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H26" s="282"/>
-      <c r="I26" s="282">
+      <c r="H26" s="219"/>
+      <c r="I26" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J26" s="282" t="str">
+      <c r="J26" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K26" s="282" t="str">
+      <c r="K26" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L26" s="283"/>
+      <c r="L26" s="220"/>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="281">
+      <c r="A27" s="218">
         <v>22</v>
       </c>
-      <c r="B27" s="267" t="s">
+      <c r="B27" s="212" t="s">
         <v>124</v>
       </c>
-      <c r="C27" s="282"/>
-      <c r="D27" s="282"/>
-      <c r="E27" s="282"/>
-      <c r="F27" s="282"/>
-      <c r="G27" s="282">
+      <c r="C27" s="219"/>
+      <c r="D27" s="219"/>
+      <c r="E27" s="219"/>
+      <c r="F27" s="219"/>
+      <c r="G27" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H27" s="282"/>
-      <c r="I27" s="282">
+      <c r="H27" s="219"/>
+      <c r="I27" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J27" s="282" t="str">
+      <c r="J27" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K27" s="282" t="str">
+      <c r="K27" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L27" s="283"/>
+      <c r="L27" s="220"/>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="281">
+      <c r="A28" s="218">
         <v>23</v>
       </c>
-      <c r="B28" s="267" t="s">
+      <c r="B28" s="212" t="s">
         <v>125</v>
       </c>
-      <c r="C28" s="282"/>
-      <c r="D28" s="282"/>
-      <c r="E28" s="282"/>
-      <c r="F28" s="282"/>
-      <c r="G28" s="282">
+      <c r="C28" s="219"/>
+      <c r="D28" s="219"/>
+      <c r="E28" s="219"/>
+      <c r="F28" s="219"/>
+      <c r="G28" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H28" s="282"/>
-      <c r="I28" s="282">
+      <c r="H28" s="219"/>
+      <c r="I28" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J28" s="282" t="str">
+      <c r="J28" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K28" s="282" t="str">
+      <c r="K28" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L28" s="283"/>
+      <c r="L28" s="220"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="281">
+      <c r="A29" s="218">
         <v>24</v>
       </c>
-      <c r="B29" s="267" t="s">
+      <c r="B29" s="212" t="s">
         <v>126</v>
       </c>
-      <c r="C29" s="282"/>
-      <c r="D29" s="282"/>
-      <c r="E29" s="282"/>
-      <c r="F29" s="282"/>
-      <c r="G29" s="282">
+      <c r="C29" s="219"/>
+      <c r="D29" s="219"/>
+      <c r="E29" s="219"/>
+      <c r="F29" s="219"/>
+      <c r="G29" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H29" s="282"/>
-      <c r="I29" s="282">
+      <c r="H29" s="219"/>
+      <c r="I29" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J29" s="282" t="str">
+      <c r="J29" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K29" s="282" t="str">
+      <c r="K29" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L29" s="283"/>
+      <c r="L29" s="220"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="281">
+      <c r="A30" s="218">
         <v>25</v>
       </c>
-      <c r="B30" s="267" t="s">
+      <c r="B30" s="212" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="282"/>
-      <c r="D30" s="282"/>
-      <c r="E30" s="282"/>
-      <c r="F30" s="282"/>
-      <c r="G30" s="282">
+      <c r="C30" s="219"/>
+      <c r="D30" s="219"/>
+      <c r="E30" s="219"/>
+      <c r="F30" s="219"/>
+      <c r="G30" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H30" s="282"/>
-      <c r="I30" s="282">
+      <c r="H30" s="219"/>
+      <c r="I30" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J30" s="282" t="str">
+      <c r="J30" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K30" s="282" t="str">
+      <c r="K30" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L30" s="283"/>
+      <c r="L30" s="220"/>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="281">
+      <c r="A31" s="218">
         <v>26</v>
       </c>
-      <c r="B31" s="267" t="s">
+      <c r="B31" s="212" t="s">
         <v>128</v>
       </c>
-      <c r="C31" s="282"/>
-      <c r="D31" s="282"/>
-      <c r="E31" s="282"/>
-      <c r="F31" s="282"/>
-      <c r="G31" s="282">
+      <c r="C31" s="219"/>
+      <c r="D31" s="219"/>
+      <c r="E31" s="219"/>
+      <c r="F31" s="219"/>
+      <c r="G31" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H31" s="282"/>
-      <c r="I31" s="282">
+      <c r="H31" s="219"/>
+      <c r="I31" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J31" s="282" t="str">
+      <c r="J31" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K31" s="282" t="str">
+      <c r="K31" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L31" s="283"/>
+      <c r="L31" s="220"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="281">
+      <c r="A32" s="218">
         <v>27</v>
       </c>
-      <c r="B32" s="267" t="s">
+      <c r="B32" s="212" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="282"/>
-      <c r="D32" s="282"/>
-      <c r="E32" s="282"/>
-      <c r="F32" s="282"/>
-      <c r="G32" s="282">
+      <c r="C32" s="219"/>
+      <c r="D32" s="219"/>
+      <c r="E32" s="219"/>
+      <c r="F32" s="219"/>
+      <c r="G32" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H32" s="282"/>
-      <c r="I32" s="282">
+      <c r="H32" s="219"/>
+      <c r="I32" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J32" s="282" t="str">
+      <c r="J32" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K32" s="282" t="str">
+      <c r="K32" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L32" s="283"/>
+      <c r="L32" s="220"/>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="281">
+      <c r="A33" s="218">
         <v>28</v>
       </c>
-      <c r="B33" s="267" t="s">
+      <c r="B33" s="212" t="s">
         <v>130</v>
       </c>
-      <c r="C33" s="282"/>
-      <c r="D33" s="282"/>
-      <c r="E33" s="282"/>
-      <c r="F33" s="282"/>
-      <c r="G33" s="282">
+      <c r="C33" s="219"/>
+      <c r="D33" s="219"/>
+      <c r="E33" s="219"/>
+      <c r="F33" s="219"/>
+      <c r="G33" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H33" s="282"/>
-      <c r="I33" s="282">
+      <c r="H33" s="219"/>
+      <c r="I33" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J33" s="282" t="str">
+      <c r="J33" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K33" s="282" t="str">
+      <c r="K33" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L33" s="283"/>
+      <c r="L33" s="220"/>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="281">
+      <c r="A34" s="218">
         <v>29</v>
       </c>
-      <c r="B34" s="267" t="s">
+      <c r="B34" s="212" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="282"/>
-      <c r="D34" s="282"/>
-      <c r="E34" s="282"/>
-      <c r="F34" s="282"/>
-      <c r="G34" s="282">
+      <c r="C34" s="219"/>
+      <c r="D34" s="219"/>
+      <c r="E34" s="219"/>
+      <c r="F34" s="219"/>
+      <c r="G34" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H34" s="282"/>
-      <c r="I34" s="282">
+      <c r="H34" s="219"/>
+      <c r="I34" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J34" s="282" t="str">
+      <c r="J34" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K34" s="282" t="str">
+      <c r="K34" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L34" s="283"/>
+      <c r="L34" s="220"/>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="281">
+      <c r="A35" s="218">
         <v>30</v>
       </c>
-      <c r="B35" s="267" t="s">
+      <c r="B35" s="212" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="282"/>
-      <c r="D35" s="282"/>
-      <c r="E35" s="282"/>
-      <c r="F35" s="282"/>
-      <c r="G35" s="282">
+      <c r="C35" s="219"/>
+      <c r="D35" s="219"/>
+      <c r="E35" s="219"/>
+      <c r="F35" s="219"/>
+      <c r="G35" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H35" s="282"/>
-      <c r="I35" s="282">
+      <c r="H35" s="219"/>
+      <c r="I35" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J35" s="282" t="str">
+      <c r="J35" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K35" s="282" t="str">
+      <c r="K35" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L35" s="283"/>
+      <c r="L35" s="220"/>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="281">
+      <c r="A36" s="218">
         <v>31</v>
       </c>
-      <c r="B36" s="267" t="s">
+      <c r="B36" s="212" t="s">
         <v>133</v>
       </c>
-      <c r="C36" s="282"/>
-      <c r="D36" s="282"/>
-      <c r="E36" s="282"/>
-      <c r="F36" s="282"/>
-      <c r="G36" s="282">
+      <c r="C36" s="219"/>
+      <c r="D36" s="219"/>
+      <c r="E36" s="219"/>
+      <c r="F36" s="219"/>
+      <c r="G36" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H36" s="282"/>
-      <c r="I36" s="282">
+      <c r="H36" s="219"/>
+      <c r="I36" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J36" s="282" t="str">
+      <c r="J36" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K36" s="282" t="str">
+      <c r="K36" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L36" s="283"/>
+      <c r="L36" s="220"/>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="281">
+      <c r="A37" s="218">
         <v>32</v>
       </c>
-      <c r="B37" s="267" t="s">
+      <c r="B37" s="212" t="s">
         <v>134</v>
       </c>
-      <c r="C37" s="282"/>
-      <c r="D37" s="282"/>
-      <c r="E37" s="282"/>
-      <c r="F37" s="282"/>
-      <c r="G37" s="282">
+      <c r="C37" s="219"/>
+      <c r="D37" s="219"/>
+      <c r="E37" s="219"/>
+      <c r="F37" s="219"/>
+      <c r="G37" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H37" s="282"/>
-      <c r="I37" s="282">
+      <c r="H37" s="219"/>
+      <c r="I37" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J37" s="282" t="str">
+      <c r="J37" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K37" s="282" t="str">
+      <c r="K37" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L37" s="283"/>
+      <c r="L37" s="220"/>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="281">
+      <c r="A38" s="218">
         <v>33</v>
       </c>
-      <c r="B38" s="267" t="s">
+      <c r="B38" s="212" t="s">
         <v>135</v>
       </c>
-      <c r="C38" s="282"/>
-      <c r="D38" s="282"/>
-      <c r="E38" s="282"/>
-      <c r="F38" s="282"/>
-      <c r="G38" s="282">
+      <c r="C38" s="219"/>
+      <c r="D38" s="219"/>
+      <c r="E38" s="219"/>
+      <c r="F38" s="219"/>
+      <c r="G38" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H38" s="282"/>
-      <c r="I38" s="282">
+      <c r="H38" s="219"/>
+      <c r="I38" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J38" s="282" t="str">
+      <c r="J38" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K38" s="282" t="str">
+      <c r="K38" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L38" s="283"/>
+      <c r="L38" s="220"/>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="281">
+      <c r="A39" s="218">
         <v>34</v>
       </c>
-      <c r="B39" s="267" t="s">
+      <c r="B39" s="212" t="s">
         <v>136</v>
       </c>
-      <c r="C39" s="282"/>
-      <c r="D39" s="282"/>
-      <c r="E39" s="282"/>
-      <c r="F39" s="282"/>
-      <c r="G39" s="282">
+      <c r="C39" s="219"/>
+      <c r="D39" s="219"/>
+      <c r="E39" s="219"/>
+      <c r="F39" s="219"/>
+      <c r="G39" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H39" s="282"/>
-      <c r="I39" s="282">
+      <c r="H39" s="219"/>
+      <c r="I39" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J39" s="282" t="str">
+      <c r="J39" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K39" s="282" t="str">
+      <c r="K39" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L39" s="283"/>
+      <c r="L39" s="220"/>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="281">
+      <c r="A40" s="218">
         <v>35</v>
       </c>
-      <c r="B40" s="267" t="s">
+      <c r="B40" s="212" t="s">
         <v>137</v>
       </c>
-      <c r="C40" s="282"/>
-      <c r="D40" s="282"/>
-      <c r="E40" s="282"/>
-      <c r="F40" s="282"/>
-      <c r="G40" s="282">
+      <c r="C40" s="219"/>
+      <c r="D40" s="219"/>
+      <c r="E40" s="219"/>
+      <c r="F40" s="219"/>
+      <c r="G40" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H40" s="282"/>
-      <c r="I40" s="282">
+      <c r="H40" s="219"/>
+      <c r="I40" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J40" s="282" t="str">
+      <c r="J40" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K40" s="282" t="str">
+      <c r="K40" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L40" s="283"/>
+      <c r="L40" s="220"/>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="281">
+      <c r="A41" s="218">
         <v>36</v>
       </c>
-      <c r="B41" s="267" t="s">
+      <c r="B41" s="212" t="s">
         <v>138</v>
       </c>
-      <c r="C41" s="282"/>
-      <c r="D41" s="282"/>
-      <c r="E41" s="282"/>
-      <c r="F41" s="282"/>
-      <c r="G41" s="282">
+      <c r="C41" s="219"/>
+      <c r="D41" s="219"/>
+      <c r="E41" s="219"/>
+      <c r="F41" s="219"/>
+      <c r="G41" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H41" s="282"/>
-      <c r="I41" s="282">
+      <c r="H41" s="219"/>
+      <c r="I41" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J41" s="282" t="str">
+      <c r="J41" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K41" s="282" t="str">
+      <c r="K41" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L41" s="283"/>
+      <c r="L41" s="220"/>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="281">
+      <c r="A42" s="218">
         <v>37</v>
       </c>
-      <c r="B42" s="267" t="s">
+      <c r="B42" s="212" t="s">
         <v>139</v>
       </c>
-      <c r="C42" s="282"/>
-      <c r="D42" s="282"/>
-      <c r="E42" s="282"/>
-      <c r="F42" s="282"/>
-      <c r="G42" s="282">
+      <c r="C42" s="219"/>
+      <c r="D42" s="219"/>
+      <c r="E42" s="219"/>
+      <c r="F42" s="219"/>
+      <c r="G42" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H42" s="282"/>
-      <c r="I42" s="282">
+      <c r="H42" s="219"/>
+      <c r="I42" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J42" s="282" t="str">
+      <c r="J42" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K42" s="282" t="str">
+      <c r="K42" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L42" s="283"/>
+      <c r="L42" s="220"/>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="281">
+      <c r="A43" s="218">
         <v>38</v>
       </c>
-      <c r="B43" s="267" t="s">
+      <c r="B43" s="212" t="s">
         <v>140</v>
       </c>
-      <c r="C43" s="282"/>
-      <c r="D43" s="282"/>
-      <c r="E43" s="282"/>
-      <c r="F43" s="282"/>
-      <c r="G43" s="282">
+      <c r="C43" s="219"/>
+      <c r="D43" s="219"/>
+      <c r="E43" s="219"/>
+      <c r="F43" s="219"/>
+      <c r="G43" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H43" s="282"/>
-      <c r="I43" s="282">
+      <c r="H43" s="219"/>
+      <c r="I43" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J43" s="282" t="str">
+      <c r="J43" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K43" s="282" t="str">
+      <c r="K43" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L43" s="283"/>
+      <c r="L43" s="220"/>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="281">
+      <c r="A44" s="218">
         <v>39</v>
       </c>
-      <c r="B44" s="267" t="s">
+      <c r="B44" s="212" t="s">
         <v>175</v>
       </c>
-      <c r="C44" s="282"/>
-      <c r="D44" s="282"/>
-      <c r="E44" s="282"/>
-      <c r="F44" s="282"/>
-      <c r="G44" s="282">
+      <c r="C44" s="219"/>
+      <c r="D44" s="219"/>
+      <c r="E44" s="219"/>
+      <c r="F44" s="219"/>
+      <c r="G44" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H44" s="282"/>
-      <c r="I44" s="282">
+      <c r="H44" s="219"/>
+      <c r="I44" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J44" s="282" t="str">
+      <c r="J44" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K44" s="282" t="str">
+      <c r="K44" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L44" s="283"/>
+      <c r="L44" s="220"/>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="281">
+      <c r="A45" s="218">
         <v>40</v>
       </c>
-      <c r="B45" s="267" t="s">
+      <c r="B45" s="212" t="s">
         <v>176</v>
       </c>
-      <c r="C45" s="282"/>
-      <c r="D45" s="282"/>
-      <c r="E45" s="282"/>
-      <c r="F45" s="282"/>
-      <c r="G45" s="282">
+      <c r="C45" s="219"/>
+      <c r="D45" s="219"/>
+      <c r="E45" s="219"/>
+      <c r="F45" s="219"/>
+      <c r="G45" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H45" s="282"/>
-      <c r="I45" s="282">
+      <c r="H45" s="219"/>
+      <c r="I45" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J45" s="282" t="str">
+      <c r="J45" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K45" s="282" t="str">
+      <c r="K45" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L45" s="283"/>
+      <c r="L45" s="220"/>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="281">
+      <c r="A46" s="218">
         <v>41</v>
       </c>
-      <c r="B46" s="267"/>
-      <c r="C46" s="282"/>
-      <c r="D46" s="282"/>
-      <c r="E46" s="282"/>
-      <c r="F46" s="282"/>
-      <c r="G46" s="282">
+      <c r="B46" s="212"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="219"/>
+      <c r="E46" s="219"/>
+      <c r="F46" s="219"/>
+      <c r="G46" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H46" s="282"/>
-      <c r="I46" s="282">
+      <c r="H46" s="219"/>
+      <c r="I46" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J46" s="282" t="str">
+      <c r="J46" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K46" s="282" t="str">
+      <c r="K46" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L46" s="283"/>
+      <c r="L46" s="220"/>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="281">
+      <c r="A47" s="218">
         <v>42</v>
       </c>
-      <c r="B47" s="284"/>
-      <c r="C47" s="282"/>
-      <c r="D47" s="282"/>
-      <c r="E47" s="282"/>
-      <c r="F47" s="282"/>
-      <c r="G47" s="282">
+      <c r="B47" s="221"/>
+      <c r="C47" s="219"/>
+      <c r="D47" s="219"/>
+      <c r="E47" s="219"/>
+      <c r="F47" s="219"/>
+      <c r="G47" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H47" s="282"/>
-      <c r="I47" s="282">
+      <c r="H47" s="219"/>
+      <c r="I47" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J47" s="282" t="str">
+      <c r="J47" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K47" s="282" t="str">
+      <c r="K47" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L47" s="283"/>
+      <c r="L47" s="220"/>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="281">
+      <c r="A48" s="218">
         <v>43</v>
       </c>
-      <c r="B48" s="284"/>
-      <c r="C48" s="282"/>
-      <c r="D48" s="282"/>
-      <c r="E48" s="282"/>
-      <c r="F48" s="282"/>
-      <c r="G48" s="282">
+      <c r="B48" s="221"/>
+      <c r="C48" s="219"/>
+      <c r="D48" s="219"/>
+      <c r="E48" s="219"/>
+      <c r="F48" s="219"/>
+      <c r="G48" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H48" s="282"/>
-      <c r="I48" s="282">
+      <c r="H48" s="219"/>
+      <c r="I48" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J48" s="282" t="str">
+      <c r="J48" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K48" s="282" t="str">
+      <c r="K48" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L48" s="283"/>
+      <c r="L48" s="220"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="281">
+      <c r="A49" s="218">
         <v>44</v>
       </c>
-      <c r="B49" s="284"/>
-      <c r="C49" s="282"/>
-      <c r="D49" s="282"/>
-      <c r="E49" s="282"/>
-      <c r="F49" s="282"/>
-      <c r="G49" s="282">
+      <c r="B49" s="221"/>
+      <c r="C49" s="219"/>
+      <c r="D49" s="219"/>
+      <c r="E49" s="219"/>
+      <c r="F49" s="219"/>
+      <c r="G49" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H49" s="282"/>
-      <c r="I49" s="282">
+      <c r="H49" s="219"/>
+      <c r="I49" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J49" s="282" t="str">
+      <c r="J49" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K49" s="282" t="str">
+      <c r="K49" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L49" s="283"/>
+      <c r="L49" s="220"/>
     </row>
     <row r="50" spans="1:12">
-      <c r="A50" s="281">
+      <c r="A50" s="218">
         <v>45</v>
       </c>
-      <c r="B50" s="282"/>
-      <c r="C50" s="282"/>
-      <c r="D50" s="282"/>
-      <c r="E50" s="282"/>
-      <c r="F50" s="282"/>
-      <c r="G50" s="282">
+      <c r="B50" s="219"/>
+      <c r="C50" s="219"/>
+      <c r="D50" s="219"/>
+      <c r="E50" s="219"/>
+      <c r="F50" s="219"/>
+      <c r="G50" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H50" s="282"/>
-      <c r="I50" s="282">
+      <c r="H50" s="219"/>
+      <c r="I50" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J50" s="282" t="str">
+      <c r="J50" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K50" s="282" t="str">
+      <c r="K50" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L50" s="283"/>
+      <c r="L50" s="220"/>
     </row>
     <row r="51" spans="1:12">
-      <c r="A51" s="281">
+      <c r="A51" s="218">
         <v>46</v>
       </c>
-      <c r="B51" s="282"/>
-      <c r="C51" s="282"/>
-      <c r="D51" s="282"/>
-      <c r="E51" s="282"/>
-      <c r="F51" s="282"/>
-      <c r="G51" s="282">
+      <c r="B51" s="219"/>
+      <c r="C51" s="219"/>
+      <c r="D51" s="219"/>
+      <c r="E51" s="219"/>
+      <c r="F51" s="219"/>
+      <c r="G51" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H51" s="282"/>
-      <c r="I51" s="282">
+      <c r="H51" s="219"/>
+      <c r="I51" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J51" s="282" t="str">
+      <c r="J51" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K51" s="282" t="str">
+      <c r="K51" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L51" s="283"/>
+      <c r="L51" s="220"/>
     </row>
     <row r="52" spans="1:12">
-      <c r="A52" s="281">
+      <c r="A52" s="218">
         <v>47</v>
       </c>
-      <c r="B52" s="282"/>
-      <c r="C52" s="282"/>
-      <c r="D52" s="282"/>
-      <c r="E52" s="282"/>
-      <c r="F52" s="282"/>
-      <c r="G52" s="282">
+      <c r="B52" s="219"/>
+      <c r="C52" s="219"/>
+      <c r="D52" s="219"/>
+      <c r="E52" s="219"/>
+      <c r="F52" s="219"/>
+      <c r="G52" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H52" s="282"/>
-      <c r="I52" s="282">
+      <c r="H52" s="219"/>
+      <c r="I52" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J52" s="282" t="str">
+      <c r="J52" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K52" s="282" t="str">
+      <c r="K52" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L52" s="283"/>
+      <c r="L52" s="220"/>
     </row>
     <row r="53" spans="1:12">
-      <c r="A53" s="281">
+      <c r="A53" s="218">
         <v>48</v>
       </c>
-      <c r="B53" s="282"/>
-      <c r="C53" s="282"/>
-      <c r="D53" s="282"/>
-      <c r="E53" s="282"/>
-      <c r="F53" s="282"/>
-      <c r="G53" s="282">
+      <c r="B53" s="219"/>
+      <c r="C53" s="219"/>
+      <c r="D53" s="219"/>
+      <c r="E53" s="219"/>
+      <c r="F53" s="219"/>
+      <c r="G53" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H53" s="282"/>
-      <c r="I53" s="282">
+      <c r="H53" s="219"/>
+      <c r="I53" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J53" s="282" t="str">
+      <c r="J53" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K53" s="282" t="str">
+      <c r="K53" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L53" s="283"/>
+      <c r="L53" s="220"/>
     </row>
     <row r="54" spans="1:12">
-      <c r="A54" s="281">
+      <c r="A54" s="218">
         <v>49</v>
       </c>
-      <c r="B54" s="282"/>
-      <c r="C54" s="282"/>
-      <c r="D54" s="282"/>
-      <c r="E54" s="282"/>
-      <c r="F54" s="282"/>
-      <c r="G54" s="282">
+      <c r="B54" s="219"/>
+      <c r="C54" s="219"/>
+      <c r="D54" s="219"/>
+      <c r="E54" s="219"/>
+      <c r="F54" s="219"/>
+      <c r="G54" s="219">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H54" s="282"/>
-      <c r="I54" s="282">
+      <c r="H54" s="219"/>
+      <c r="I54" s="219">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J54" s="282" t="str">
+      <c r="J54" s="219" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K54" s="282" t="str">
+      <c r="K54" s="219" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L54" s="283"/>
+      <c r="L54" s="220"/>
     </row>
     <row r="55" spans="1:12" ht="15.75" thickBot="1">
-      <c r="A55" s="285">
+      <c r="A55" s="222">
         <v>50</v>
       </c>
-      <c r="B55" s="286"/>
-      <c r="C55" s="286"/>
-      <c r="D55" s="286"/>
-      <c r="E55" s="286"/>
-      <c r="F55" s="286"/>
-      <c r="G55" s="286">
+      <c r="B55" s="223"/>
+      <c r="C55" s="223"/>
+      <c r="D55" s="223"/>
+      <c r="E55" s="223"/>
+      <c r="F55" s="223"/>
+      <c r="G55" s="223">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H55" s="286"/>
-      <c r="I55" s="286">
+      <c r="H55" s="223"/>
+      <c r="I55" s="223">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J55" s="286" t="str">
+      <c r="J55" s="223" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="K55" s="286" t="str">
+      <c r="K55" s="223" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="L55" s="287"/>
+      <c r="L55" s="224"/>
     </row>
   </sheetData>
   <sheetProtection formatColumns="0"/>
@@ -47245,7 +47250,7 @@
     <col min="21" max="22" width="11.140625" style="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="75">
+    <row r="1" spans="1:22" ht="74.25">
       <c r="A1" s="180" t="s">
         <v>178</v>
       </c>
@@ -49463,7 +49468,7 @@
       </c>
       <c r="D26" s="3">
         <f>Scoresheet!AG27</f>
-        <v>144</v>
+        <v>84</v>
       </c>
       <c r="E26" s="3">
         <f>Scoresheet!AS27</f>
@@ -49527,11 +49532,11 @@
       </c>
       <c r="T26" s="3">
         <f t="shared" si="1"/>
-        <v>1484</v>
+        <v>1424</v>
       </c>
       <c r="U26" s="125">
         <f t="shared" si="2"/>
-        <v>87.294117647058826</v>
+        <v>83.764705882352942</v>
       </c>
       <c r="V26" s="188">
         <f t="shared" si="0"/>
